--- a/Stok Kontrol/Eklenen.xlsx
+++ b/Stok Kontrol/Eklenen.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Stok Kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD6CE38-7F9D-478E-9720-C1272BF5504A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4FAB23-8342-46CF-8281-008B6F5A3588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="186">
   <si>
     <t>BARKOD NUMARASI</t>
   </si>
@@ -414,9 +425,6 @@
     <t>000000000040003685</t>
   </si>
   <si>
-    <t>88838900-2</t>
-  </si>
-  <si>
     <t>000000000040002586</t>
   </si>
   <si>
@@ -424,6 +432,168 @@
   </si>
   <si>
     <t>000000000040002271</t>
+  </si>
+  <si>
+    <t>89465300-10</t>
+  </si>
+  <si>
+    <t>000000000040002162</t>
+  </si>
+  <si>
+    <t>89465900-1</t>
+  </si>
+  <si>
+    <t>000000000040002214</t>
+  </si>
+  <si>
+    <t>89330900-1</t>
+  </si>
+  <si>
+    <t>000000000040000821</t>
+  </si>
+  <si>
+    <t>89331000-2</t>
+  </si>
+  <si>
+    <t>000000000040003362</t>
+  </si>
+  <si>
+    <t>89331000-3</t>
+  </si>
+  <si>
+    <t>89331000-5</t>
+  </si>
+  <si>
+    <t>89331000-4</t>
+  </si>
+  <si>
+    <t>89331000-1</t>
+  </si>
+  <si>
+    <t>89331200-4</t>
+  </si>
+  <si>
+    <t>000000000040003502</t>
+  </si>
+  <si>
+    <t>89331200-2</t>
+  </si>
+  <si>
+    <t>89331200-5</t>
+  </si>
+  <si>
+    <t>89331200-3</t>
+  </si>
+  <si>
+    <t>89331200-1</t>
+  </si>
+  <si>
+    <t>89331100-5</t>
+  </si>
+  <si>
+    <t>000000000040003505</t>
+  </si>
+  <si>
+    <t>89331100-2</t>
+  </si>
+  <si>
+    <t>89331100-4</t>
+  </si>
+  <si>
+    <t>89331100-3</t>
+  </si>
+  <si>
+    <t>89331100-1</t>
+  </si>
+  <si>
+    <t>89369400-15</t>
+  </si>
+  <si>
+    <t>000000000040002160</t>
+  </si>
+  <si>
+    <t>68177000-330</t>
+  </si>
+  <si>
+    <t>40002679</t>
+  </si>
+  <si>
+    <t>89467500-1</t>
+  </si>
+  <si>
+    <t>88580700-9</t>
+  </si>
+  <si>
+    <t>40002559</t>
+  </si>
+  <si>
+    <t>89370900-1</t>
+  </si>
+  <si>
+    <t>40002139</t>
+  </si>
+  <si>
+    <t>89466900-9</t>
+  </si>
+  <si>
+    <t>40002378</t>
+  </si>
+  <si>
+    <t>89389300-12</t>
+  </si>
+  <si>
+    <t>40002399</t>
+  </si>
+  <si>
+    <t>89344500-2</t>
+  </si>
+  <si>
+    <t>000000000045029797</t>
+  </si>
+  <si>
+    <t>89344500-3</t>
+  </si>
+  <si>
+    <t>89344500-1</t>
+  </si>
+  <si>
+    <t>89344500-4</t>
+  </si>
+  <si>
+    <t>89372100-2</t>
+  </si>
+  <si>
+    <t>000000000045003662</t>
+  </si>
+  <si>
+    <t>89262600-3</t>
+  </si>
+  <si>
+    <t>000000000045007460</t>
+  </si>
+  <si>
+    <t>89324800-1</t>
+  </si>
+  <si>
+    <t>000000000045001665</t>
+  </si>
+  <si>
+    <t>40002417</t>
+  </si>
+  <si>
+    <t>40002156</t>
+  </si>
+  <si>
+    <t>89366900-2</t>
+  </si>
+  <si>
+    <t>89369800-27</t>
+  </si>
+  <si>
+    <t>40002152</t>
+  </si>
+  <si>
+    <t>88462400-295</t>
   </si>
 </sst>
 </file>
@@ -459,10 +629,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -483,8 +656,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}" name="EKLENEN" displayName="EKLENEN" ref="A1:E97" totalsRowShown="0">
-  <autoFilter ref="A1:E97" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}" name="EKLENEN" displayName="EKLENEN" ref="A1:E131" totalsRowShown="0">
+  <autoFilter ref="A1:E131" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{C7FC6704-65BD-4F1E-AB57-95E929157E58}" name="BARKOD NUMARASI"/>
     <tableColumn id="2" xr3:uid="{BD785338-7565-42D3-ADE5-4B20FE7C87B3}" name="ÜRÜN KODU / ÜRÜN TANIMI"/>
@@ -759,7 +932,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2384,10 +2557,10 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>160</v>
+      </c>
+      <c r="B96" t="s">
         <v>129</v>
-      </c>
-      <c r="B96" t="s">
-        <v>130</v>
       </c>
       <c r="C96">
         <v>72000</v>
@@ -2401,10 +2574,10 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>130</v>
+      </c>
+      <c r="B97" t="s">
         <v>131</v>
-      </c>
-      <c r="B97" t="s">
-        <v>132</v>
       </c>
       <c r="C97">
         <v>4200</v>
@@ -2414,6 +2587,560 @@
       </c>
       <c r="E97" s="2">
         <v>46120</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>132</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C98">
+        <v>1860</v>
+      </c>
+      <c r="D98" t="s">
+        <v>6</v>
+      </c>
+      <c r="E98" s="2">
+        <v>46120</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>134</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C99">
+        <v>25700</v>
+      </c>
+      <c r="D99" t="s">
+        <v>6</v>
+      </c>
+      <c r="E99" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>136</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C100">
+        <v>16230</v>
+      </c>
+      <c r="D100" t="s">
+        <v>6</v>
+      </c>
+      <c r="E100" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>138</v>
+      </c>
+      <c r="B101" t="s">
+        <v>139</v>
+      </c>
+      <c r="C101">
+        <v>16656</v>
+      </c>
+      <c r="D101" t="s">
+        <v>6</v>
+      </c>
+      <c r="E101" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>140</v>
+      </c>
+      <c r="B102" t="s">
+        <v>139</v>
+      </c>
+      <c r="C102">
+        <v>16656</v>
+      </c>
+      <c r="D102" t="s">
+        <v>6</v>
+      </c>
+      <c r="E102" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>141</v>
+      </c>
+      <c r="B103" t="s">
+        <v>139</v>
+      </c>
+      <c r="C103">
+        <v>16656</v>
+      </c>
+      <c r="D103" t="s">
+        <v>6</v>
+      </c>
+      <c r="E103" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>142</v>
+      </c>
+      <c r="B104" t="s">
+        <v>139</v>
+      </c>
+      <c r="C104">
+        <v>16656</v>
+      </c>
+      <c r="D104" t="s">
+        <v>6</v>
+      </c>
+      <c r="E104" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>143</v>
+      </c>
+      <c r="B105" t="s">
+        <v>139</v>
+      </c>
+      <c r="C105">
+        <v>16656</v>
+      </c>
+      <c r="D105" t="s">
+        <v>6</v>
+      </c>
+      <c r="E105" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>144</v>
+      </c>
+      <c r="B106" t="s">
+        <v>145</v>
+      </c>
+      <c r="C106">
+        <v>16764</v>
+      </c>
+      <c r="D106" t="s">
+        <v>6</v>
+      </c>
+      <c r="E106" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>146</v>
+      </c>
+      <c r="B107" t="s">
+        <v>145</v>
+      </c>
+      <c r="C107">
+        <v>16764</v>
+      </c>
+      <c r="D107" t="s">
+        <v>6</v>
+      </c>
+      <c r="E107" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>147</v>
+      </c>
+      <c r="B108" t="s">
+        <v>145</v>
+      </c>
+      <c r="C108">
+        <v>16764</v>
+      </c>
+      <c r="D108" t="s">
+        <v>6</v>
+      </c>
+      <c r="E108" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>148</v>
+      </c>
+      <c r="B109" t="s">
+        <v>145</v>
+      </c>
+      <c r="C109">
+        <v>16764</v>
+      </c>
+      <c r="D109" t="s">
+        <v>6</v>
+      </c>
+      <c r="E109" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>149</v>
+      </c>
+      <c r="B110" t="s">
+        <v>145</v>
+      </c>
+      <c r="C110">
+        <v>16764</v>
+      </c>
+      <c r="D110" t="s">
+        <v>6</v>
+      </c>
+      <c r="E110" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>150</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C111">
+        <v>16775</v>
+      </c>
+      <c r="D111" t="s">
+        <v>6</v>
+      </c>
+      <c r="E111" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>152</v>
+      </c>
+      <c r="B112" t="s">
+        <v>151</v>
+      </c>
+      <c r="C112">
+        <v>16775</v>
+      </c>
+      <c r="D112" t="s">
+        <v>6</v>
+      </c>
+      <c r="E112" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>153</v>
+      </c>
+      <c r="B113" t="s">
+        <v>151</v>
+      </c>
+      <c r="C113">
+        <v>16775</v>
+      </c>
+      <c r="D113" t="s">
+        <v>6</v>
+      </c>
+      <c r="E113" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>154</v>
+      </c>
+      <c r="B114" t="s">
+        <v>151</v>
+      </c>
+      <c r="C114">
+        <v>16775</v>
+      </c>
+      <c r="D114" t="s">
+        <v>6</v>
+      </c>
+      <c r="E114" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>155</v>
+      </c>
+      <c r="B115" t="s">
+        <v>151</v>
+      </c>
+      <c r="C115">
+        <v>16775</v>
+      </c>
+      <c r="D115" t="s">
+        <v>6</v>
+      </c>
+      <c r="E115" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>156</v>
+      </c>
+      <c r="B116" t="s">
+        <v>157</v>
+      </c>
+      <c r="C116">
+        <v>342</v>
+      </c>
+      <c r="D116" t="s">
+        <v>6</v>
+      </c>
+      <c r="E116" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>158</v>
+      </c>
+      <c r="B117" t="s">
+        <v>159</v>
+      </c>
+      <c r="C117">
+        <v>4954</v>
+      </c>
+      <c r="E117" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>161</v>
+      </c>
+      <c r="B118" t="s">
+        <v>162</v>
+      </c>
+      <c r="C118">
+        <v>12107</v>
+      </c>
+      <c r="E118" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>163</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C119">
+        <v>12016</v>
+      </c>
+      <c r="E119" s="2">
+        <v>46121</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>165</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C120">
+        <v>5000</v>
+      </c>
+      <c r="E120" s="2">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>167</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C121">
+        <v>2200</v>
+      </c>
+      <c r="E121" s="2">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>169</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C122">
+        <v>524</v>
+      </c>
+      <c r="D122" t="s">
+        <v>6</v>
+      </c>
+      <c r="E122" s="2">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>171</v>
+      </c>
+      <c r="B123" t="s">
+        <v>170</v>
+      </c>
+      <c r="C123">
+        <v>524</v>
+      </c>
+      <c r="D123" t="s">
+        <v>6</v>
+      </c>
+      <c r="E123" s="2">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>172</v>
+      </c>
+      <c r="B124" t="s">
+        <v>170</v>
+      </c>
+      <c r="C124">
+        <v>524</v>
+      </c>
+      <c r="D124" t="s">
+        <v>6</v>
+      </c>
+      <c r="E124" s="2">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>173</v>
+      </c>
+      <c r="B125" t="s">
+        <v>170</v>
+      </c>
+      <c r="C125">
+        <v>524</v>
+      </c>
+      <c r="D125" t="s">
+        <v>6</v>
+      </c>
+      <c r="E125" s="2">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>174</v>
+      </c>
+      <c r="B126" t="s">
+        <v>175</v>
+      </c>
+      <c r="C126">
+        <v>3000</v>
+      </c>
+      <c r="D126" t="s">
+        <v>6</v>
+      </c>
+      <c r="E126" s="2">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>176</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C127">
+        <v>4352</v>
+      </c>
+      <c r="D127" t="s">
+        <v>6</v>
+      </c>
+      <c r="E127" s="2">
+        <v>46125</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>178</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C128">
+        <v>1200</v>
+      </c>
+      <c r="D128" t="s">
+        <v>6</v>
+      </c>
+      <c r="E128" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>182</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C129">
+        <v>20067</v>
+      </c>
+      <c r="E129" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>183</v>
+      </c>
+      <c r="B130" t="s">
+        <v>181</v>
+      </c>
+      <c r="C130">
+        <v>4022</v>
+      </c>
+      <c r="E130" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>185</v>
+      </c>
+      <c r="B131" t="s">
+        <v>184</v>
+      </c>
+      <c r="C131">
+        <v>6759</v>
+      </c>
+      <c r="E131" s="2">
+        <v>46126</v>
       </c>
     </row>
   </sheetData>

--- a/Stok Kontrol/Eklenen.xlsx
+++ b/Stok Kontrol/Eklenen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Stok Kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4FAB23-8342-46CF-8281-008B6F5A3588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6D44DE-9187-41FC-8645-FB094F3FDCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="329">
   <si>
     <t>BARKOD NUMARASI</t>
   </si>
@@ -594,6 +594,435 @@
   </si>
   <si>
     <t>88462400-295</t>
+  </si>
+  <si>
+    <t>89386900-17</t>
+  </si>
+  <si>
+    <t>000000000040002352</t>
+  </si>
+  <si>
+    <t>89455600-56</t>
+  </si>
+  <si>
+    <t>89456200-51</t>
+  </si>
+  <si>
+    <t>000000000040000813</t>
+  </si>
+  <si>
+    <t>89466500-1</t>
+  </si>
+  <si>
+    <t>89466500-3</t>
+  </si>
+  <si>
+    <t>89466500-4</t>
+  </si>
+  <si>
+    <t>89466500-5</t>
+  </si>
+  <si>
+    <t>89466500-6</t>
+  </si>
+  <si>
+    <t>89466500-7</t>
+  </si>
+  <si>
+    <t>89466500-8</t>
+  </si>
+  <si>
+    <t>89466500-9</t>
+  </si>
+  <si>
+    <t>89466500-2</t>
+  </si>
+  <si>
+    <t>89383600-5</t>
+  </si>
+  <si>
+    <t>000000000040002076</t>
+  </si>
+  <si>
+    <t>89383600-1</t>
+  </si>
+  <si>
+    <t>89383600-4</t>
+  </si>
+  <si>
+    <t>89383600-2</t>
+  </si>
+  <si>
+    <t>89383600-3</t>
+  </si>
+  <si>
+    <t>89383600-6</t>
+  </si>
+  <si>
+    <t>89383500-1</t>
+  </si>
+  <si>
+    <t>000000000040002080</t>
+  </si>
+  <si>
+    <t>89430500-1</t>
+  </si>
+  <si>
+    <t>000000000040000570</t>
+  </si>
+  <si>
+    <t>89386900-13</t>
+  </si>
+  <si>
+    <t>89370100-111</t>
+  </si>
+  <si>
+    <t>000000000040002152</t>
+  </si>
+  <si>
+    <t>89345800-34</t>
+  </si>
+  <si>
+    <t>000000000040002500</t>
+  </si>
+  <si>
+    <t>89465500-41</t>
+  </si>
+  <si>
+    <t>000000000040002348</t>
+  </si>
+  <si>
+    <t>89371100-262</t>
+  </si>
+  <si>
+    <t>000000000040002136</t>
+  </si>
+  <si>
+    <t>89393350-1</t>
+  </si>
+  <si>
+    <t>89468300-1</t>
+  </si>
+  <si>
+    <t>89468300-2</t>
+  </si>
+  <si>
+    <t>89468300-3</t>
+  </si>
+  <si>
+    <t>89468300-4</t>
+  </si>
+  <si>
+    <t>89468300-5</t>
+  </si>
+  <si>
+    <t>89468300-6</t>
+  </si>
+  <si>
+    <t>89468300-7</t>
+  </si>
+  <si>
+    <t>89468300-8</t>
+  </si>
+  <si>
+    <t>89389200-5</t>
+  </si>
+  <si>
+    <t>000000000040002432</t>
+  </si>
+  <si>
+    <t>89466500-10</t>
+  </si>
+  <si>
+    <t>89463300-1</t>
+  </si>
+  <si>
+    <t>000000000040002090</t>
+  </si>
+  <si>
+    <t>89463400-6</t>
+  </si>
+  <si>
+    <t>000000000040002086</t>
+  </si>
+  <si>
+    <t>89463400-9</t>
+  </si>
+  <si>
+    <t>89463400-11</t>
+  </si>
+  <si>
+    <t>89463400-15</t>
+  </si>
+  <si>
+    <t>89463400-16</t>
+  </si>
+  <si>
+    <t>89463400-18</t>
+  </si>
+  <si>
+    <t>89469800-2</t>
+  </si>
+  <si>
+    <t>000000000040002287</t>
+  </si>
+  <si>
+    <t>89369200-2070</t>
+  </si>
+  <si>
+    <t>89537800-11</t>
+  </si>
+  <si>
+    <t>000000000040002515</t>
+  </si>
+  <si>
+    <t>89466900-41</t>
+  </si>
+  <si>
+    <t>000000000040002378</t>
+  </si>
+  <si>
+    <t>89369900-71</t>
+  </si>
+  <si>
+    <t>000000000040003158</t>
+  </si>
+  <si>
+    <t>71662800-10</t>
+  </si>
+  <si>
+    <t>000000000040001143</t>
+  </si>
+  <si>
+    <t>88068300-25</t>
+  </si>
+  <si>
+    <t>000000000040002102</t>
+  </si>
+  <si>
+    <t>74031100-32</t>
+  </si>
+  <si>
+    <t>000000000040001775</t>
+  </si>
+  <si>
+    <t>88756400-2</t>
+  </si>
+  <si>
+    <t>000000000040001414</t>
+  </si>
+  <si>
+    <t>84744800-8</t>
+  </si>
+  <si>
+    <t>000000000040001427</t>
+  </si>
+  <si>
+    <t>74031100-33</t>
+  </si>
+  <si>
+    <t>88756400-3</t>
+  </si>
+  <si>
+    <t>89505000-8</t>
+  </si>
+  <si>
+    <t>000000000040001638</t>
+  </si>
+  <si>
+    <t>81219200-3</t>
+  </si>
+  <si>
+    <t>000000000040001674</t>
+  </si>
+  <si>
+    <t>74039600-3</t>
+  </si>
+  <si>
+    <t>000000000040000936</t>
+  </si>
+  <si>
+    <t>74031100-34</t>
+  </si>
+  <si>
+    <t>74031100-35</t>
+  </si>
+  <si>
+    <t>89498500-43</t>
+  </si>
+  <si>
+    <t>000000000040001639</t>
+  </si>
+  <si>
+    <t>88068300-26</t>
+  </si>
+  <si>
+    <t>69592500-15</t>
+  </si>
+  <si>
+    <t>000000000040001256</t>
+  </si>
+  <si>
+    <t>69592500-16</t>
+  </si>
+  <si>
+    <t>89523100-2</t>
+  </si>
+  <si>
+    <t>000000000040000664</t>
+  </si>
+  <si>
+    <t>89354200-2</t>
+  </si>
+  <si>
+    <t>000000000040001037</t>
+  </si>
+  <si>
+    <t>89523100-3</t>
+  </si>
+  <si>
+    <t>89523100-4</t>
+  </si>
+  <si>
+    <t>89495300-2</t>
+  </si>
+  <si>
+    <t>000000000040000770</t>
+  </si>
+  <si>
+    <t>89523100-5</t>
+  </si>
+  <si>
+    <t>88756400-4</t>
+  </si>
+  <si>
+    <t>89407600-28</t>
+  </si>
+  <si>
+    <t>000000000040001118</t>
+  </si>
+  <si>
+    <t>87821500-2</t>
+  </si>
+  <si>
+    <t>000000000040002114</t>
+  </si>
+  <si>
+    <t>89354200-3</t>
+  </si>
+  <si>
+    <t>69592500-17</t>
+  </si>
+  <si>
+    <t>69592500-18</t>
+  </si>
+  <si>
+    <t>69592500-19</t>
+  </si>
+  <si>
+    <t>69592500-20</t>
+  </si>
+  <si>
+    <t>87831100-2</t>
+  </si>
+  <si>
+    <t>000000000040002106</t>
+  </si>
+  <si>
+    <t>87831100-3</t>
+  </si>
+  <si>
+    <t>81154000-64</t>
+  </si>
+  <si>
+    <t>000000000040002129</t>
+  </si>
+  <si>
+    <t>88065200-2</t>
+  </si>
+  <si>
+    <t>000000000040002108</t>
+  </si>
+  <si>
+    <t>73257300-69</t>
+  </si>
+  <si>
+    <t>000000000040001449</t>
+  </si>
+  <si>
+    <t>88579300-193</t>
+  </si>
+  <si>
+    <t>000000000040000939</t>
+  </si>
+  <si>
+    <t>89250400-29</t>
+  </si>
+  <si>
+    <t>000000000040001869</t>
+  </si>
+  <si>
+    <t>69592500-21</t>
+  </si>
+  <si>
+    <t>88065200-3</t>
+  </si>
+  <si>
+    <t>84379300-113</t>
+  </si>
+  <si>
+    <t>000000000040000906</t>
+  </si>
+  <si>
+    <t>89286600-15</t>
+  </si>
+  <si>
+    <t>000000000040001386</t>
+  </si>
+  <si>
+    <t>81217900-7</t>
+  </si>
+  <si>
+    <t>000000000040002116</t>
+  </si>
+  <si>
+    <t>87822800-2</t>
+  </si>
+  <si>
+    <t>000000000040002089</t>
+  </si>
+  <si>
+    <t>89343100-3</t>
+  </si>
+  <si>
+    <t>000000000040001008</t>
+  </si>
+  <si>
+    <t>89490500-15</t>
+  </si>
+  <si>
+    <t>000000000040001404</t>
+  </si>
+  <si>
+    <t>88065200-4</t>
+  </si>
+  <si>
+    <t>88065200-5</t>
+  </si>
+  <si>
+    <t>89398500-109</t>
+  </si>
+  <si>
+    <t>000000000040000775</t>
+  </si>
+  <si>
+    <t>89409300-2</t>
+  </si>
+  <si>
+    <t>000000000040001149</t>
+  </si>
+  <si>
+    <t>89464800-13</t>
   </si>
 </sst>
 </file>
@@ -617,7 +1046,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -625,17 +1054,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -656,8 +1107,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}" name="EKLENEN" displayName="EKLENEN" ref="A1:E131" totalsRowShown="0">
-  <autoFilter ref="A1:E131" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}" name="EKLENEN" displayName="EKLENEN" ref="A1:E229" totalsRowShown="0">
+  <autoFilter ref="A1:E229" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{C7FC6704-65BD-4F1E-AB57-95E929157E58}" name="BARKOD NUMARASI"/>
     <tableColumn id="2" xr3:uid="{BD785338-7565-42D3-ADE5-4B20FE7C87B3}" name="ÜRÜN KODU / ÜRÜN TANIMI"/>
@@ -932,12 +1383,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E229"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="28.5703125" customWidth="1"/>
     <col min="3" max="3" width="10.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -3141,6 +3593,1606 @@
       </c>
       <c r="E131" s="2">
         <v>46126</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>186</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C132">
+        <v>7500</v>
+      </c>
+      <c r="D132" t="s">
+        <v>6</v>
+      </c>
+      <c r="E132" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>188</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C133" s="1">
+        <v>5586</v>
+      </c>
+      <c r="E133" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>189</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C134" s="1">
+        <v>5586</v>
+      </c>
+      <c r="E134" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>191</v>
+      </c>
+      <c r="B135">
+        <v>40002466</v>
+      </c>
+      <c r="C135">
+        <v>68000</v>
+      </c>
+      <c r="E135" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>192</v>
+      </c>
+      <c r="B136">
+        <v>40002466</v>
+      </c>
+      <c r="C136">
+        <v>70000</v>
+      </c>
+      <c r="E136" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>193</v>
+      </c>
+      <c r="B137">
+        <v>40002466</v>
+      </c>
+      <c r="C137">
+        <v>69000</v>
+      </c>
+      <c r="E137" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>194</v>
+      </c>
+      <c r="B138">
+        <v>40002466</v>
+      </c>
+      <c r="C138">
+        <v>62000</v>
+      </c>
+      <c r="E138" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>195</v>
+      </c>
+      <c r="B139">
+        <v>40002466</v>
+      </c>
+      <c r="C139">
+        <v>70000</v>
+      </c>
+      <c r="E139" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>196</v>
+      </c>
+      <c r="B140">
+        <v>40002466</v>
+      </c>
+      <c r="C140">
+        <v>70176</v>
+      </c>
+      <c r="E140" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>197</v>
+      </c>
+      <c r="B141">
+        <v>40002466</v>
+      </c>
+      <c r="C141">
+        <v>70000</v>
+      </c>
+      <c r="E141" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>198</v>
+      </c>
+      <c r="B142">
+        <v>40002466</v>
+      </c>
+      <c r="C142">
+        <v>70176</v>
+      </c>
+      <c r="E142" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>199</v>
+      </c>
+      <c r="B143">
+        <v>40002466</v>
+      </c>
+      <c r="C143">
+        <v>71000</v>
+      </c>
+      <c r="E143" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>200</v>
+      </c>
+      <c r="B144" t="s">
+        <v>201</v>
+      </c>
+      <c r="C144">
+        <v>2274</v>
+      </c>
+      <c r="D144" t="s">
+        <v>6</v>
+      </c>
+      <c r="E144" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>202</v>
+      </c>
+      <c r="B145" t="s">
+        <v>201</v>
+      </c>
+      <c r="C145">
+        <v>2274</v>
+      </c>
+      <c r="D145" t="s">
+        <v>6</v>
+      </c>
+      <c r="E145" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>203</v>
+      </c>
+      <c r="B146" t="s">
+        <v>201</v>
+      </c>
+      <c r="C146">
+        <v>2274</v>
+      </c>
+      <c r="D146" t="s">
+        <v>6</v>
+      </c>
+      <c r="E146" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>204</v>
+      </c>
+      <c r="B147" t="s">
+        <v>201</v>
+      </c>
+      <c r="C147">
+        <v>2274</v>
+      </c>
+      <c r="D147" t="s">
+        <v>6</v>
+      </c>
+      <c r="E147" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>205</v>
+      </c>
+      <c r="B148" t="s">
+        <v>201</v>
+      </c>
+      <c r="C148">
+        <v>2274</v>
+      </c>
+      <c r="D148" t="s">
+        <v>6</v>
+      </c>
+      <c r="E148" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>206</v>
+      </c>
+      <c r="B149" t="s">
+        <v>201</v>
+      </c>
+      <c r="C149">
+        <v>2274</v>
+      </c>
+      <c r="D149" t="s">
+        <v>6</v>
+      </c>
+      <c r="E149" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>207</v>
+      </c>
+      <c r="B150" t="s">
+        <v>208</v>
+      </c>
+      <c r="C150">
+        <v>2216</v>
+      </c>
+      <c r="D150" t="s">
+        <v>6</v>
+      </c>
+      <c r="E150" s="2">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>209</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C151">
+        <v>35009</v>
+      </c>
+      <c r="D151" t="s">
+        <v>6</v>
+      </c>
+      <c r="E151" s="2">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>211</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C152">
+        <v>15000</v>
+      </c>
+      <c r="D152" t="s">
+        <v>6</v>
+      </c>
+      <c r="E152" s="2">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>212</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C153">
+        <v>540</v>
+      </c>
+      <c r="D153" t="s">
+        <v>6</v>
+      </c>
+      <c r="E153" s="2">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>214</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C154">
+        <v>17550</v>
+      </c>
+      <c r="D154" t="s">
+        <v>6</v>
+      </c>
+      <c r="E154" s="2">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>216</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C155">
+        <v>6400</v>
+      </c>
+      <c r="D155" t="s">
+        <v>6</v>
+      </c>
+      <c r="E155" s="2">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>218</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C156">
+        <v>34557</v>
+      </c>
+      <c r="D156" t="s">
+        <v>6</v>
+      </c>
+      <c r="E156" s="2">
+        <v>46128</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>220</v>
+      </c>
+      <c r="B157">
+        <v>45018489</v>
+      </c>
+      <c r="C157">
+        <v>426</v>
+      </c>
+      <c r="E157" s="2">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>221</v>
+      </c>
+      <c r="B158">
+        <v>40003268</v>
+      </c>
+      <c r="C158">
+        <v>9100</v>
+      </c>
+      <c r="E158" s="2">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>222</v>
+      </c>
+      <c r="B159">
+        <v>40003268</v>
+      </c>
+      <c r="C159">
+        <v>9200</v>
+      </c>
+      <c r="E159" s="2">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>223</v>
+      </c>
+      <c r="B160">
+        <v>40003268</v>
+      </c>
+      <c r="C160">
+        <v>9250</v>
+      </c>
+      <c r="E160" s="2">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>224</v>
+      </c>
+      <c r="B161">
+        <v>40003268</v>
+      </c>
+      <c r="C161">
+        <v>9200</v>
+      </c>
+      <c r="E161" s="2">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>225</v>
+      </c>
+      <c r="B162">
+        <v>40003268</v>
+      </c>
+      <c r="C162">
+        <v>9100</v>
+      </c>
+      <c r="E162" s="2">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>226</v>
+      </c>
+      <c r="B163">
+        <v>40003268</v>
+      </c>
+      <c r="C163">
+        <v>9200</v>
+      </c>
+      <c r="E163" s="2">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>227</v>
+      </c>
+      <c r="B164">
+        <v>40003268</v>
+      </c>
+      <c r="C164">
+        <v>9300</v>
+      </c>
+      <c r="E164" s="2">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>228</v>
+      </c>
+      <c r="B165">
+        <v>40003268</v>
+      </c>
+      <c r="C165">
+        <v>9200</v>
+      </c>
+      <c r="E165" s="2">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>229</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C166">
+        <v>6110</v>
+      </c>
+      <c r="D166" t="s">
+        <v>6</v>
+      </c>
+      <c r="E166" s="2">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>231</v>
+      </c>
+      <c r="B167">
+        <v>40002466</v>
+      </c>
+      <c r="C167">
+        <v>70176</v>
+      </c>
+      <c r="E167" s="2">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>232</v>
+      </c>
+      <c r="B168" t="s">
+        <v>233</v>
+      </c>
+      <c r="C168">
+        <v>16890</v>
+      </c>
+      <c r="D168" t="s">
+        <v>6</v>
+      </c>
+      <c r="E168" s="2">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>234</v>
+      </c>
+      <c r="B169" t="s">
+        <v>235</v>
+      </c>
+      <c r="C169">
+        <v>5783</v>
+      </c>
+      <c r="D169" t="s">
+        <v>6</v>
+      </c>
+      <c r="E169" s="2">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>236</v>
+      </c>
+      <c r="B170" t="s">
+        <v>235</v>
+      </c>
+      <c r="C170">
+        <v>5783</v>
+      </c>
+      <c r="D170" t="s">
+        <v>6</v>
+      </c>
+      <c r="E170" s="2">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>237</v>
+      </c>
+      <c r="B171" t="s">
+        <v>235</v>
+      </c>
+      <c r="C171">
+        <v>5783</v>
+      </c>
+      <c r="D171" t="s">
+        <v>6</v>
+      </c>
+      <c r="E171" s="2">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>238</v>
+      </c>
+      <c r="B172" t="s">
+        <v>235</v>
+      </c>
+      <c r="C172">
+        <v>5783</v>
+      </c>
+      <c r="D172" t="s">
+        <v>6</v>
+      </c>
+      <c r="E172" s="2">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>239</v>
+      </c>
+      <c r="B173" t="s">
+        <v>235</v>
+      </c>
+      <c r="C173">
+        <v>5783</v>
+      </c>
+      <c r="D173" t="s">
+        <v>6</v>
+      </c>
+      <c r="E173" s="2">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>240</v>
+      </c>
+      <c r="B174" t="s">
+        <v>235</v>
+      </c>
+      <c r="C174">
+        <v>5783</v>
+      </c>
+      <c r="D174" t="s">
+        <v>6</v>
+      </c>
+      <c r="E174" s="2">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>241</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C175">
+        <v>2400</v>
+      </c>
+      <c r="D175" t="s">
+        <v>6</v>
+      </c>
+      <c r="E175" s="2">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>243</v>
+      </c>
+      <c r="B176" t="s">
+        <v>119</v>
+      </c>
+      <c r="C176">
+        <v>1532</v>
+      </c>
+      <c r="E176" s="2">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>244</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C177">
+        <v>3100</v>
+      </c>
+      <c r="D177" t="s">
+        <v>6</v>
+      </c>
+      <c r="E177" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C178">
+        <v>3100</v>
+      </c>
+      <c r="D178" t="s">
+        <v>6</v>
+      </c>
+      <c r="E178" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C179">
+        <v>110527</v>
+      </c>
+      <c r="D179" t="s">
+        <v>6</v>
+      </c>
+      <c r="E179" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C180">
+        <v>14382</v>
+      </c>
+      <c r="D180" t="s">
+        <v>6</v>
+      </c>
+      <c r="E180" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>252</v>
+      </c>
+      <c r="B181" t="s">
+        <v>253</v>
+      </c>
+      <c r="C181">
+        <v>23945</v>
+      </c>
+      <c r="D181" t="s">
+        <v>6</v>
+      </c>
+      <c r="E181" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>254</v>
+      </c>
+      <c r="B182" t="s">
+        <v>255</v>
+      </c>
+      <c r="C182">
+        <v>4361</v>
+      </c>
+      <c r="D182" t="s">
+        <v>6</v>
+      </c>
+      <c r="E182" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>256</v>
+      </c>
+      <c r="B183" t="s">
+        <v>257</v>
+      </c>
+      <c r="C183">
+        <v>4553</v>
+      </c>
+      <c r="D183" t="s">
+        <v>6</v>
+      </c>
+      <c r="E183" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>258</v>
+      </c>
+      <c r="B184" t="s">
+        <v>259</v>
+      </c>
+      <c r="C184">
+        <v>3820</v>
+      </c>
+      <c r="D184" t="s">
+        <v>6</v>
+      </c>
+      <c r="E184" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>260</v>
+      </c>
+      <c r="B185" t="s">
+        <v>255</v>
+      </c>
+      <c r="C185">
+        <v>4425</v>
+      </c>
+      <c r="D185" t="s">
+        <v>6</v>
+      </c>
+      <c r="E185" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>261</v>
+      </c>
+      <c r="B186" t="s">
+        <v>257</v>
+      </c>
+      <c r="C186">
+        <v>4425</v>
+      </c>
+      <c r="D186" t="s">
+        <v>6</v>
+      </c>
+      <c r="E186" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>262</v>
+      </c>
+      <c r="B187" t="s">
+        <v>263</v>
+      </c>
+      <c r="C187">
+        <v>6128</v>
+      </c>
+      <c r="D187" t="s">
+        <v>6</v>
+      </c>
+      <c r="E187" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>264</v>
+      </c>
+      <c r="B188" t="s">
+        <v>265</v>
+      </c>
+      <c r="C188">
+        <v>3443</v>
+      </c>
+      <c r="D188" t="s">
+        <v>6</v>
+      </c>
+      <c r="E188" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>266</v>
+      </c>
+      <c r="B189" t="s">
+        <v>267</v>
+      </c>
+      <c r="C189">
+        <v>2306</v>
+      </c>
+      <c r="D189" t="s">
+        <v>6</v>
+      </c>
+      <c r="E189" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>268</v>
+      </c>
+      <c r="B190" t="s">
+        <v>255</v>
+      </c>
+      <c r="C190">
+        <v>4425</v>
+      </c>
+      <c r="D190" t="s">
+        <v>6</v>
+      </c>
+      <c r="E190" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>269</v>
+      </c>
+      <c r="B191" t="s">
+        <v>255</v>
+      </c>
+      <c r="C191">
+        <v>5067</v>
+      </c>
+      <c r="D191" t="s">
+        <v>6</v>
+      </c>
+      <c r="E191" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>270</v>
+      </c>
+      <c r="B192" t="s">
+        <v>271</v>
+      </c>
+      <c r="C192">
+        <v>8360</v>
+      </c>
+      <c r="D192" t="s">
+        <v>6</v>
+      </c>
+      <c r="E192" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>272</v>
+      </c>
+      <c r="B193" t="s">
+        <v>253</v>
+      </c>
+      <c r="C193">
+        <v>4018</v>
+      </c>
+      <c r="D193" t="s">
+        <v>6</v>
+      </c>
+      <c r="E193" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>273</v>
+      </c>
+      <c r="B194" t="s">
+        <v>274</v>
+      </c>
+      <c r="C194">
+        <v>6731</v>
+      </c>
+      <c r="D194" t="s">
+        <v>6</v>
+      </c>
+      <c r="E194" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>275</v>
+      </c>
+      <c r="B195" t="s">
+        <v>274</v>
+      </c>
+      <c r="C195">
+        <v>6436</v>
+      </c>
+      <c r="D195" t="s">
+        <v>6</v>
+      </c>
+      <c r="E195" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>276</v>
+      </c>
+      <c r="B196" t="s">
+        <v>277</v>
+      </c>
+      <c r="C196">
+        <v>3362</v>
+      </c>
+      <c r="D196" t="s">
+        <v>6</v>
+      </c>
+      <c r="E196" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>278</v>
+      </c>
+      <c r="B197" t="s">
+        <v>279</v>
+      </c>
+      <c r="C197">
+        <v>3362</v>
+      </c>
+      <c r="D197" t="s">
+        <v>6</v>
+      </c>
+      <c r="E197" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>280</v>
+      </c>
+      <c r="B198" t="s">
+        <v>277</v>
+      </c>
+      <c r="C198">
+        <v>3362</v>
+      </c>
+      <c r="D198" t="s">
+        <v>6</v>
+      </c>
+      <c r="E198" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>281</v>
+      </c>
+      <c r="B199" t="s">
+        <v>277</v>
+      </c>
+      <c r="C199">
+        <v>3362</v>
+      </c>
+      <c r="D199" t="s">
+        <v>6</v>
+      </c>
+      <c r="E199" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>282</v>
+      </c>
+      <c r="B200" t="s">
+        <v>283</v>
+      </c>
+      <c r="C200">
+        <v>3362</v>
+      </c>
+      <c r="D200" t="s">
+        <v>6</v>
+      </c>
+      <c r="E200" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>284</v>
+      </c>
+      <c r="B201" t="s">
+        <v>277</v>
+      </c>
+      <c r="C201">
+        <v>3362</v>
+      </c>
+      <c r="D201" t="s">
+        <v>6</v>
+      </c>
+      <c r="E201" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>285</v>
+      </c>
+      <c r="B202" t="s">
+        <v>257</v>
+      </c>
+      <c r="C202">
+        <v>2277</v>
+      </c>
+      <c r="D202" t="s">
+        <v>6</v>
+      </c>
+      <c r="E202" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>286</v>
+      </c>
+      <c r="B203" t="s">
+        <v>287</v>
+      </c>
+      <c r="C203">
+        <v>6926</v>
+      </c>
+      <c r="D203" t="s">
+        <v>6</v>
+      </c>
+      <c r="E203" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>288</v>
+      </c>
+      <c r="B204" t="s">
+        <v>289</v>
+      </c>
+      <c r="C204">
+        <v>2424</v>
+      </c>
+      <c r="D204" t="s">
+        <v>6</v>
+      </c>
+      <c r="E204" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>290</v>
+      </c>
+      <c r="B205" t="s">
+        <v>279</v>
+      </c>
+      <c r="C205">
+        <v>2944</v>
+      </c>
+      <c r="D205" t="s">
+        <v>6</v>
+      </c>
+      <c r="E205" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>291</v>
+      </c>
+      <c r="B206" t="s">
+        <v>274</v>
+      </c>
+      <c r="C206">
+        <v>7204</v>
+      </c>
+      <c r="D206" t="s">
+        <v>6</v>
+      </c>
+      <c r="E206" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>292</v>
+      </c>
+      <c r="B207" t="s">
+        <v>274</v>
+      </c>
+      <c r="C207">
+        <v>6731</v>
+      </c>
+      <c r="D207" t="s">
+        <v>6</v>
+      </c>
+      <c r="E207" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>293</v>
+      </c>
+      <c r="B208" t="s">
+        <v>274</v>
+      </c>
+      <c r="C208">
+        <v>6926</v>
+      </c>
+      <c r="D208" t="s">
+        <v>6</v>
+      </c>
+      <c r="E208" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>294</v>
+      </c>
+      <c r="B209" t="s">
+        <v>274</v>
+      </c>
+      <c r="C209">
+        <v>6628</v>
+      </c>
+      <c r="D209" t="s">
+        <v>6</v>
+      </c>
+      <c r="E209" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>295</v>
+      </c>
+      <c r="B210" t="s">
+        <v>296</v>
+      </c>
+      <c r="C210">
+        <v>3276</v>
+      </c>
+      <c r="D210" t="s">
+        <v>6</v>
+      </c>
+      <c r="E210" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>297</v>
+      </c>
+      <c r="B211" t="s">
+        <v>296</v>
+      </c>
+      <c r="C211">
+        <v>2982</v>
+      </c>
+      <c r="D211" t="s">
+        <v>6</v>
+      </c>
+      <c r="E211" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>298</v>
+      </c>
+      <c r="B212" t="s">
+        <v>299</v>
+      </c>
+      <c r="C212">
+        <v>2738</v>
+      </c>
+      <c r="D212" t="s">
+        <v>6</v>
+      </c>
+      <c r="E212" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>300</v>
+      </c>
+      <c r="B213" t="s">
+        <v>301</v>
+      </c>
+      <c r="C213">
+        <v>3236</v>
+      </c>
+      <c r="D213" t="s">
+        <v>6</v>
+      </c>
+      <c r="E213" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>302</v>
+      </c>
+      <c r="B214" t="s">
+        <v>303</v>
+      </c>
+      <c r="C214">
+        <v>981</v>
+      </c>
+      <c r="D214" t="s">
+        <v>6</v>
+      </c>
+      <c r="E214" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>304</v>
+      </c>
+      <c r="B215" t="s">
+        <v>305</v>
+      </c>
+      <c r="C215">
+        <v>692</v>
+      </c>
+      <c r="D215" t="s">
+        <v>6</v>
+      </c>
+      <c r="E215" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>306</v>
+      </c>
+      <c r="B216" t="s">
+        <v>307</v>
+      </c>
+      <c r="C216">
+        <v>3276</v>
+      </c>
+      <c r="D216" t="s">
+        <v>6</v>
+      </c>
+      <c r="E216" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>308</v>
+      </c>
+      <c r="B217" t="s">
+        <v>274</v>
+      </c>
+      <c r="C217">
+        <v>6926</v>
+      </c>
+      <c r="D217" t="s">
+        <v>6</v>
+      </c>
+      <c r="E217" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>309</v>
+      </c>
+      <c r="B218" t="s">
+        <v>301</v>
+      </c>
+      <c r="C218">
+        <v>1983</v>
+      </c>
+      <c r="D218" t="s">
+        <v>6</v>
+      </c>
+      <c r="E218" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>310</v>
+      </c>
+      <c r="B219" t="s">
+        <v>311</v>
+      </c>
+      <c r="C219">
+        <v>1692</v>
+      </c>
+      <c r="D219" t="s">
+        <v>6</v>
+      </c>
+      <c r="E219" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>312</v>
+      </c>
+      <c r="B220" t="s">
+        <v>313</v>
+      </c>
+      <c r="C220">
+        <v>2943</v>
+      </c>
+      <c r="D220" t="s">
+        <v>6</v>
+      </c>
+      <c r="E220" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>314</v>
+      </c>
+      <c r="B221" t="s">
+        <v>315</v>
+      </c>
+      <c r="C221">
+        <v>1176</v>
+      </c>
+      <c r="D221" t="s">
+        <v>6</v>
+      </c>
+      <c r="E221" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>316</v>
+      </c>
+      <c r="B222" t="s">
+        <v>317</v>
+      </c>
+      <c r="C222">
+        <v>4429</v>
+      </c>
+      <c r="D222" t="s">
+        <v>6</v>
+      </c>
+      <c r="E222" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>318</v>
+      </c>
+      <c r="B223" t="s">
+        <v>319</v>
+      </c>
+      <c r="C223">
+        <v>6727</v>
+      </c>
+      <c r="D223" t="s">
+        <v>6</v>
+      </c>
+      <c r="E223" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>320</v>
+      </c>
+      <c r="B224" t="s">
+        <v>321</v>
+      </c>
+      <c r="C224">
+        <v>3450</v>
+      </c>
+      <c r="D224" t="s">
+        <v>6</v>
+      </c>
+      <c r="E224" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>322</v>
+      </c>
+      <c r="B225" t="s">
+        <v>301</v>
+      </c>
+      <c r="C225">
+        <v>3097</v>
+      </c>
+      <c r="D225" t="s">
+        <v>6</v>
+      </c>
+      <c r="E225" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>323</v>
+      </c>
+      <c r="B226" t="s">
+        <v>301</v>
+      </c>
+      <c r="C226">
+        <v>3236</v>
+      </c>
+      <c r="D226" t="s">
+        <v>6</v>
+      </c>
+      <c r="E226" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>324</v>
+      </c>
+      <c r="B227" t="s">
+        <v>325</v>
+      </c>
+      <c r="C227">
+        <v>2092</v>
+      </c>
+      <c r="D227" t="s">
+        <v>6</v>
+      </c>
+      <c r="E227" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>326</v>
+      </c>
+      <c r="B228" t="s">
+        <v>327</v>
+      </c>
+      <c r="C228">
+        <v>3715</v>
+      </c>
+      <c r="D228" t="s">
+        <v>6</v>
+      </c>
+      <c r="E228" s="2">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>328</v>
+      </c>
+      <c r="B229" t="s">
+        <v>235</v>
+      </c>
+      <c r="C229">
+        <v>3532</v>
+      </c>
+      <c r="D229" t="s">
+        <v>6</v>
+      </c>
+      <c r="E229" s="2">
+        <v>46133</v>
       </c>
     </row>
   </sheetData>

--- a/Stok Kontrol/Eklenen.xlsx
+++ b/Stok Kontrol/Eklenen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Stok Kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6D44DE-9187-41FC-8645-FB094F3FDCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D12C2A-EFA0-4636-9C67-69D7F94E653C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="364">
   <si>
     <t>BARKOD NUMARASI</t>
   </si>
@@ -1023,6 +1023,111 @@
   </si>
   <si>
     <t>89464800-13</t>
+  </si>
+  <si>
+    <t>89470700-21</t>
+  </si>
+  <si>
+    <t>000000000040002728</t>
+  </si>
+  <si>
+    <t>89424600-13</t>
+  </si>
+  <si>
+    <t>000000000040003594</t>
+  </si>
+  <si>
+    <t>89424600-9</t>
+  </si>
+  <si>
+    <t>89424600-8</t>
+  </si>
+  <si>
+    <t>89424600-2</t>
+  </si>
+  <si>
+    <t>89424600-12</t>
+  </si>
+  <si>
+    <t>89424600-3</t>
+  </si>
+  <si>
+    <t>89424400-5</t>
+  </si>
+  <si>
+    <t>000000000040003506</t>
+  </si>
+  <si>
+    <t>89424400-12</t>
+  </si>
+  <si>
+    <t>89424400-9</t>
+  </si>
+  <si>
+    <t>89424400-11</t>
+  </si>
+  <si>
+    <t>89424400-3</t>
+  </si>
+  <si>
+    <t>89424400-7</t>
+  </si>
+  <si>
+    <t>89424800-14</t>
+  </si>
+  <si>
+    <t>000000000040000836</t>
+  </si>
+  <si>
+    <t>89424800-20</t>
+  </si>
+  <si>
+    <t>89424800-18</t>
+  </si>
+  <si>
+    <t>89424800-16</t>
+  </si>
+  <si>
+    <t>89424800-11</t>
+  </si>
+  <si>
+    <t>89424800-13</t>
+  </si>
+  <si>
+    <t>89424800-7</t>
+  </si>
+  <si>
+    <t>89424800-2</t>
+  </si>
+  <si>
+    <t>89424800-10</t>
+  </si>
+  <si>
+    <t>89424800-15</t>
+  </si>
+  <si>
+    <t>89424800-17</t>
+  </si>
+  <si>
+    <t>89424800-4</t>
+  </si>
+  <si>
+    <t>89424200-2</t>
+  </si>
+  <si>
+    <t>000000000040000842</t>
+  </si>
+  <si>
+    <t>89462900-1</t>
+  </si>
+  <si>
+    <t>000000000040002074</t>
+  </si>
+  <si>
+    <t>000000000040002442</t>
+  </si>
+  <si>
+    <t>89486000-20</t>
   </si>
 </sst>
 </file>
@@ -1107,8 +1212,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}" name="EKLENEN" displayName="EKLENEN" ref="A1:E229" totalsRowShown="0">
-  <autoFilter ref="A1:E229" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}" name="EKLENEN" displayName="EKLENEN" ref="A1:E257" totalsRowShown="0">
+  <autoFilter ref="A1:E257" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{C7FC6704-65BD-4F1E-AB57-95E929157E58}" name="BARKOD NUMARASI"/>
     <tableColumn id="2" xr3:uid="{BD785338-7565-42D3-ADE5-4B20FE7C87B3}" name="ÜRÜN KODU / ÜRÜN TANIMI"/>
@@ -1383,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E229"/>
+  <dimension ref="A1:E257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -5195,6 +5300,482 @@
         <v>46133</v>
       </c>
     </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C230">
+        <v>7110</v>
+      </c>
+      <c r="D230" t="s">
+        <v>6</v>
+      </c>
+      <c r="E230" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C231">
+        <v>4522</v>
+      </c>
+      <c r="D231" t="s">
+        <v>6</v>
+      </c>
+      <c r="E231" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>333</v>
+      </c>
+      <c r="B232" t="s">
+        <v>332</v>
+      </c>
+      <c r="C232">
+        <v>4522</v>
+      </c>
+      <c r="D232" t="s">
+        <v>6</v>
+      </c>
+      <c r="E232" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>334</v>
+      </c>
+      <c r="B233" t="s">
+        <v>332</v>
+      </c>
+      <c r="C233">
+        <v>4522</v>
+      </c>
+      <c r="D233" t="s">
+        <v>6</v>
+      </c>
+      <c r="E233" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>335</v>
+      </c>
+      <c r="B234" t="s">
+        <v>332</v>
+      </c>
+      <c r="C234">
+        <v>4522</v>
+      </c>
+      <c r="D234" t="s">
+        <v>6</v>
+      </c>
+      <c r="E234" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>336</v>
+      </c>
+      <c r="B235" t="s">
+        <v>332</v>
+      </c>
+      <c r="C235">
+        <v>4522</v>
+      </c>
+      <c r="D235" t="s">
+        <v>6</v>
+      </c>
+      <c r="E235" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>337</v>
+      </c>
+      <c r="B236" t="s">
+        <v>332</v>
+      </c>
+      <c r="C236">
+        <v>4522</v>
+      </c>
+      <c r="D236" t="s">
+        <v>6</v>
+      </c>
+      <c r="E236" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>338</v>
+      </c>
+      <c r="B237" t="s">
+        <v>339</v>
+      </c>
+      <c r="C237">
+        <v>4452</v>
+      </c>
+      <c r="D237" t="s">
+        <v>6</v>
+      </c>
+      <c r="E237" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>340</v>
+      </c>
+      <c r="B238" t="s">
+        <v>339</v>
+      </c>
+      <c r="C238">
+        <v>4452</v>
+      </c>
+      <c r="D238" t="s">
+        <v>6</v>
+      </c>
+      <c r="E238" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>341</v>
+      </c>
+      <c r="B239" t="s">
+        <v>339</v>
+      </c>
+      <c r="C239">
+        <v>4452</v>
+      </c>
+      <c r="D239" t="s">
+        <v>6</v>
+      </c>
+      <c r="E239" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>342</v>
+      </c>
+      <c r="B240" t="s">
+        <v>339</v>
+      </c>
+      <c r="C240">
+        <v>4452</v>
+      </c>
+      <c r="D240" t="s">
+        <v>6</v>
+      </c>
+      <c r="E240" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>343</v>
+      </c>
+      <c r="B241" t="s">
+        <v>339</v>
+      </c>
+      <c r="C241">
+        <v>4452</v>
+      </c>
+      <c r="D241" t="s">
+        <v>6</v>
+      </c>
+      <c r="E241" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>344</v>
+      </c>
+      <c r="B242" t="s">
+        <v>339</v>
+      </c>
+      <c r="C242">
+        <v>4452</v>
+      </c>
+      <c r="D242" t="s">
+        <v>6</v>
+      </c>
+      <c r="E242" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>345</v>
+      </c>
+      <c r="B243" t="s">
+        <v>346</v>
+      </c>
+      <c r="C243">
+        <v>4582</v>
+      </c>
+      <c r="D243" t="s">
+        <v>6</v>
+      </c>
+      <c r="E243" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>347</v>
+      </c>
+      <c r="B244" t="s">
+        <v>346</v>
+      </c>
+      <c r="C244">
+        <v>4582</v>
+      </c>
+      <c r="D244" t="s">
+        <v>6</v>
+      </c>
+      <c r="E244" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>348</v>
+      </c>
+      <c r="B245" t="s">
+        <v>346</v>
+      </c>
+      <c r="C245">
+        <v>4582</v>
+      </c>
+      <c r="D245" t="s">
+        <v>6</v>
+      </c>
+      <c r="E245" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>349</v>
+      </c>
+      <c r="B246" t="s">
+        <v>346</v>
+      </c>
+      <c r="C246">
+        <v>4582</v>
+      </c>
+      <c r="D246" t="s">
+        <v>6</v>
+      </c>
+      <c r="E246" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>350</v>
+      </c>
+      <c r="B247" t="s">
+        <v>346</v>
+      </c>
+      <c r="C247">
+        <v>4582</v>
+      </c>
+      <c r="D247" t="s">
+        <v>6</v>
+      </c>
+      <c r="E247" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>351</v>
+      </c>
+      <c r="B248" t="s">
+        <v>346</v>
+      </c>
+      <c r="C248">
+        <v>4582</v>
+      </c>
+      <c r="D248" t="s">
+        <v>6</v>
+      </c>
+      <c r="E248" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>352</v>
+      </c>
+      <c r="B249" t="s">
+        <v>346</v>
+      </c>
+      <c r="C249">
+        <v>4582</v>
+      </c>
+      <c r="D249" t="s">
+        <v>6</v>
+      </c>
+      <c r="E249" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>353</v>
+      </c>
+      <c r="B250" t="s">
+        <v>346</v>
+      </c>
+      <c r="C250">
+        <v>4582</v>
+      </c>
+      <c r="D250" t="s">
+        <v>6</v>
+      </c>
+      <c r="E250" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>354</v>
+      </c>
+      <c r="B251" t="s">
+        <v>346</v>
+      </c>
+      <c r="C251">
+        <v>4582</v>
+      </c>
+      <c r="D251" t="s">
+        <v>6</v>
+      </c>
+      <c r="E251" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>355</v>
+      </c>
+      <c r="B252" t="s">
+        <v>346</v>
+      </c>
+      <c r="C252">
+        <v>4582</v>
+      </c>
+      <c r="D252" t="s">
+        <v>6</v>
+      </c>
+      <c r="E252" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>356</v>
+      </c>
+      <c r="B253" t="s">
+        <v>346</v>
+      </c>
+      <c r="C253">
+        <v>4582</v>
+      </c>
+      <c r="D253" t="s">
+        <v>6</v>
+      </c>
+      <c r="E253" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>357</v>
+      </c>
+      <c r="B254" t="s">
+        <v>346</v>
+      </c>
+      <c r="C254">
+        <v>4582</v>
+      </c>
+      <c r="D254" t="s">
+        <v>6</v>
+      </c>
+      <c r="E254" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>358</v>
+      </c>
+      <c r="B255" t="s">
+        <v>359</v>
+      </c>
+      <c r="C255">
+        <v>4325</v>
+      </c>
+      <c r="D255" t="s">
+        <v>6</v>
+      </c>
+      <c r="E255" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A256" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C256">
+        <v>8829</v>
+      </c>
+      <c r="D256" t="s">
+        <v>6</v>
+      </c>
+      <c r="E256" s="2">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A257" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C257">
+        <v>29350</v>
+      </c>
+      <c r="D257" t="s">
+        <v>6</v>
+      </c>
+      <c r="E257" s="2">
+        <v>46134</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Stok Kontrol/Eklenen.xlsx
+++ b/Stok Kontrol/Eklenen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Stok Kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A8DD23-0201-4806-A1C3-6982C31DA154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4BE518-E882-472B-9649-A37A659428A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="33">
   <si>
     <t>BARKOD NUMARASI</t>
   </si>
@@ -81,6 +81,60 @@
   </si>
   <si>
     <t>89547700-12</t>
+  </si>
+  <si>
+    <t>89369500-19</t>
+  </si>
+  <si>
+    <t>000000000040002159</t>
+  </si>
+  <si>
+    <t>000000000040002072</t>
+  </si>
+  <si>
+    <t>89558500-3</t>
+  </si>
+  <si>
+    <t>89582400-1</t>
+  </si>
+  <si>
+    <t>89607900-201</t>
+  </si>
+  <si>
+    <t>000000000040002136</t>
+  </si>
+  <si>
+    <t>89530800-15</t>
+  </si>
+  <si>
+    <t>000000000040002444</t>
+  </si>
+  <si>
+    <t>89530800-14</t>
+  </si>
+  <si>
+    <t>89365800-20</t>
+  </si>
+  <si>
+    <t>000000000040002441</t>
+  </si>
+  <si>
+    <t>89551100-4</t>
+  </si>
+  <si>
+    <t>000000000040000825</t>
+  </si>
+  <si>
+    <t>89549400-9</t>
+  </si>
+  <si>
+    <t>000000000040002545</t>
+  </si>
+  <si>
+    <t>89584600-14</t>
+  </si>
+  <si>
+    <t>000000000040002063</t>
   </si>
 </sst>
 </file>
@@ -140,8 +194,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}" name="EKLENEN" displayName="EKLENEN" ref="A1:E7" totalsRowShown="0">
-  <autoFilter ref="A1:E7" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}" name="EKLENEN" displayName="EKLENEN" ref="A1:E17" totalsRowShown="0">
+  <autoFilter ref="A1:E17" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{C7FC6704-65BD-4F1E-AB57-95E929157E58}" name="BARKOD NUMARASI"/>
     <tableColumn id="2" xr3:uid="{BD785338-7565-42D3-ADE5-4B20FE7C87B3}" name="ÜRÜN KODU / ÜRÜN TANIMI"/>
@@ -416,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -544,6 +598,176 @@
         <v>46146</v>
       </c>
     </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>2870</v>
+      </c>
+      <c r="D8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>2686</v>
+      </c>
+      <c r="D9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10">
+        <v>1108</v>
+      </c>
+      <c r="D10" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11">
+        <v>17137</v>
+      </c>
+      <c r="D11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12">
+        <v>54310</v>
+      </c>
+      <c r="D12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13">
+        <v>45000</v>
+      </c>
+      <c r="D13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14">
+        <v>110000</v>
+      </c>
+      <c r="D14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15">
+        <v>30583</v>
+      </c>
+      <c r="D15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16">
+        <v>121520</v>
+      </c>
+      <c r="D16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="2">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17">
+        <v>4380</v>
+      </c>
+      <c r="D17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="2">
+        <v>46148</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Stok Kontrol/Eklenen.xlsx
+++ b/Stok Kontrol/Eklenen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Stok Kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4BE518-E882-472B-9649-A37A659428A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C138DF92-7584-454F-AD5A-E2B3D1AFB75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="123">
   <si>
     <t>BARKOD NUMARASI</t>
   </si>
@@ -135,6 +135,276 @@
   </si>
   <si>
     <t>000000000040002063</t>
+  </si>
+  <si>
+    <t>89550502-3</t>
+  </si>
+  <si>
+    <t>000000000045044520</t>
+  </si>
+  <si>
+    <t>89605800-201</t>
+  </si>
+  <si>
+    <t>000000000040002165</t>
+  </si>
+  <si>
+    <t>89605800-202</t>
+  </si>
+  <si>
+    <t>89605800-203</t>
+  </si>
+  <si>
+    <t>89605800-204</t>
+  </si>
+  <si>
+    <t>89537900-13</t>
+  </si>
+  <si>
+    <t>000000000040003660</t>
+  </si>
+  <si>
+    <t>89550501-7</t>
+  </si>
+  <si>
+    <t>72915700-247</t>
+  </si>
+  <si>
+    <t>000000000040002990</t>
+  </si>
+  <si>
+    <t>000000000040002596</t>
+  </si>
+  <si>
+    <t>89265400-19</t>
+  </si>
+  <si>
+    <t>89572200-2</t>
+  </si>
+  <si>
+    <t>000000000040001605</t>
+  </si>
+  <si>
+    <t>89572200-3</t>
+  </si>
+  <si>
+    <t>89572200-4</t>
+  </si>
+  <si>
+    <t>89572200-5</t>
+  </si>
+  <si>
+    <t>89572200-6</t>
+  </si>
+  <si>
+    <t>89572200-7</t>
+  </si>
+  <si>
+    <t>89572300-16</t>
+  </si>
+  <si>
+    <t>000000000040001633</t>
+  </si>
+  <si>
+    <t>89572300-42</t>
+  </si>
+  <si>
+    <t>89642200-1</t>
+  </si>
+  <si>
+    <t>000000000040003269</t>
+  </si>
+  <si>
+    <t>89555400-2</t>
+  </si>
+  <si>
+    <t>000000000040002050</t>
+  </si>
+  <si>
+    <t>89555400-1</t>
+  </si>
+  <si>
+    <t>89555400-3</t>
+  </si>
+  <si>
+    <t>89555400-5</t>
+  </si>
+  <si>
+    <t>89555400-4</t>
+  </si>
+  <si>
+    <t>89555000-2</t>
+  </si>
+  <si>
+    <t>000000000040002054</t>
+  </si>
+  <si>
+    <t>89555000-3</t>
+  </si>
+  <si>
+    <t>89555000-4</t>
+  </si>
+  <si>
+    <t>89555000-1</t>
+  </si>
+  <si>
+    <t>89555000-5</t>
+  </si>
+  <si>
+    <t>89555200-1</t>
+  </si>
+  <si>
+    <t>000000000040002061</t>
+  </si>
+  <si>
+    <t>89555200-5</t>
+  </si>
+  <si>
+    <t>89555200-2</t>
+  </si>
+  <si>
+    <t>89555200-4</t>
+  </si>
+  <si>
+    <t>89555200-3</t>
+  </si>
+  <si>
+    <t>89555600-1</t>
+  </si>
+  <si>
+    <t>000000000040001841</t>
+  </si>
+  <si>
+    <t>89555600-2</t>
+  </si>
+  <si>
+    <t>89555600-3</t>
+  </si>
+  <si>
+    <t>89555600-6</t>
+  </si>
+  <si>
+    <t>89555600-8</t>
+  </si>
+  <si>
+    <t>89555600-12</t>
+  </si>
+  <si>
+    <t>89555600-9</t>
+  </si>
+  <si>
+    <t>89555600-11</t>
+  </si>
+  <si>
+    <t>89555600-7</t>
+  </si>
+  <si>
+    <t>89555600-4</t>
+  </si>
+  <si>
+    <t>89554800-1</t>
+  </si>
+  <si>
+    <t>000000000040002044</t>
+  </si>
+  <si>
+    <t>89608300-11</t>
+  </si>
+  <si>
+    <t>000000000040002783</t>
+  </si>
+  <si>
+    <t>89547700-8</t>
+  </si>
+  <si>
+    <t>89578900-5</t>
+  </si>
+  <si>
+    <t>000000000040000991</t>
+  </si>
+  <si>
+    <t>89606800-52</t>
+  </si>
+  <si>
+    <t>000000000040003158</t>
+  </si>
+  <si>
+    <t>89585000-20</t>
+  </si>
+  <si>
+    <t>000000000040002064</t>
+  </si>
+  <si>
+    <t>89572000-1</t>
+  </si>
+  <si>
+    <t>000000000040001623</t>
+  </si>
+  <si>
+    <t>89567100-4</t>
+  </si>
+  <si>
+    <t>000000000040000626</t>
+  </si>
+  <si>
+    <t>89567200-100</t>
+  </si>
+  <si>
+    <t>000000000040000668</t>
+  </si>
+  <si>
+    <t>89567200-103</t>
+  </si>
+  <si>
+    <t>89567200-104</t>
+  </si>
+  <si>
+    <t>89567200-105</t>
+  </si>
+  <si>
+    <t>89561100-2</t>
+  </si>
+  <si>
+    <t>000000000045054909</t>
+  </si>
+  <si>
+    <t>89561100-3</t>
+  </si>
+  <si>
+    <t>89550300-20</t>
+  </si>
+  <si>
+    <t>000000000045054335</t>
+  </si>
+  <si>
+    <t>000000000045003613</t>
+  </si>
+  <si>
+    <t>89551500-9</t>
+  </si>
+  <si>
+    <t>89572300-5</t>
+  </si>
+  <si>
+    <t>89530800-23</t>
+  </si>
+  <si>
+    <t>89596101-9</t>
+  </si>
+  <si>
+    <t>000000000045054815</t>
+  </si>
+  <si>
+    <t>89588600-2</t>
+  </si>
+  <si>
+    <t>000000000040002653</t>
+  </si>
+  <si>
+    <t>89596500-5</t>
+  </si>
+  <si>
+    <t>000000000040000839</t>
   </si>
 </sst>
 </file>
@@ -194,8 +464,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}" name="EKLENEN" displayName="EKLENEN" ref="A1:E17" totalsRowShown="0">
-  <autoFilter ref="A1:E17" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}" name="EKLENEN" displayName="EKLENEN" ref="A1:E81" totalsRowShown="0">
+  <autoFilter ref="A1:E81" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{C7FC6704-65BD-4F1E-AB57-95E929157E58}" name="BARKOD NUMARASI"/>
     <tableColumn id="2" xr3:uid="{BD785338-7565-42D3-ADE5-4B20FE7C87B3}" name="ÜRÜN KODU / ÜRÜN TANIMI"/>
@@ -470,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -768,6 +1038,1094 @@
         <v>46148</v>
       </c>
     </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18">
+        <v>4367</v>
+      </c>
+      <c r="D18" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="2">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19">
+        <v>1930</v>
+      </c>
+      <c r="D19" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="2">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20">
+        <v>1980</v>
+      </c>
+      <c r="D20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="2">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21">
+        <v>1950</v>
+      </c>
+      <c r="D21" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="2">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22">
+        <v>1960</v>
+      </c>
+      <c r="D22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="2">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23">
+        <v>31055</v>
+      </c>
+      <c r="D23" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="2">
+        <v>46148</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C24">
+        <v>4367</v>
+      </c>
+      <c r="D24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="2">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25">
+        <v>7301</v>
+      </c>
+      <c r="D25" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="2">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26">
+        <v>21800</v>
+      </c>
+      <c r="D26" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="2">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27">
+        <v>14961</v>
+      </c>
+      <c r="D27" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="2">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28">
+        <v>14961</v>
+      </c>
+      <c r="D28" t="s">
+        <v>4</v>
+      </c>
+      <c r="E28" s="2">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29">
+        <v>14961</v>
+      </c>
+      <c r="D29" t="s">
+        <v>4</v>
+      </c>
+      <c r="E29" s="2">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30">
+        <v>14961</v>
+      </c>
+      <c r="D30" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" s="2">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31">
+        <v>14961</v>
+      </c>
+      <c r="D31" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" s="2">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32">
+        <v>14961</v>
+      </c>
+      <c r="D32" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="2">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33">
+        <v>5062</v>
+      </c>
+      <c r="D33" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="2">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34">
+        <v>5062</v>
+      </c>
+      <c r="D34" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" s="2">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35">
+        <v>4796</v>
+      </c>
+      <c r="D35" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36">
+        <v>2192</v>
+      </c>
+      <c r="D36" t="s">
+        <v>4</v>
+      </c>
+      <c r="E36" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37">
+        <v>2192</v>
+      </c>
+      <c r="D37" t="s">
+        <v>4</v>
+      </c>
+      <c r="E37" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38">
+        <v>2192</v>
+      </c>
+      <c r="D38" t="s">
+        <v>4</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B39" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39">
+        <v>2192</v>
+      </c>
+      <c r="D39" t="s">
+        <v>4</v>
+      </c>
+      <c r="E39" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40">
+        <v>2192</v>
+      </c>
+      <c r="D40" t="s">
+        <v>4</v>
+      </c>
+      <c r="E40" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41">
+        <v>2177</v>
+      </c>
+      <c r="D41" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>67</v>
+      </c>
+      <c r="B42" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42">
+        <v>2177</v>
+      </c>
+      <c r="D42" t="s">
+        <v>4</v>
+      </c>
+      <c r="E42" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>68</v>
+      </c>
+      <c r="B43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43">
+        <v>2177</v>
+      </c>
+      <c r="D43" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>69</v>
+      </c>
+      <c r="B44" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44">
+        <v>2177</v>
+      </c>
+      <c r="D44" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45">
+        <v>2177</v>
+      </c>
+      <c r="D45" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" t="s">
+        <v>72</v>
+      </c>
+      <c r="C46">
+        <v>2192</v>
+      </c>
+      <c r="D46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E46" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>73</v>
+      </c>
+      <c r="B47" t="s">
+        <v>72</v>
+      </c>
+      <c r="C47">
+        <v>2192</v>
+      </c>
+      <c r="D47" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>74</v>
+      </c>
+      <c r="B48" t="s">
+        <v>72</v>
+      </c>
+      <c r="C48">
+        <v>2192</v>
+      </c>
+      <c r="D48" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>75</v>
+      </c>
+      <c r="B49" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49">
+        <v>2192</v>
+      </c>
+      <c r="D49" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>76</v>
+      </c>
+      <c r="B50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50">
+        <v>2192</v>
+      </c>
+      <c r="D50" t="s">
+        <v>4</v>
+      </c>
+      <c r="E50" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>77</v>
+      </c>
+      <c r="B51" t="s">
+        <v>78</v>
+      </c>
+      <c r="C51">
+        <v>2235</v>
+      </c>
+      <c r="D51" t="s">
+        <v>4</v>
+      </c>
+      <c r="E51" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" t="s">
+        <v>78</v>
+      </c>
+      <c r="C52">
+        <v>2235</v>
+      </c>
+      <c r="D52" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" t="s">
+        <v>78</v>
+      </c>
+      <c r="C53">
+        <v>2235</v>
+      </c>
+      <c r="D53" t="s">
+        <v>4</v>
+      </c>
+      <c r="E53" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>81</v>
+      </c>
+      <c r="B54" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54">
+        <v>2235</v>
+      </c>
+      <c r="D54" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>82</v>
+      </c>
+      <c r="B55" t="s">
+        <v>78</v>
+      </c>
+      <c r="C55">
+        <v>2235</v>
+      </c>
+      <c r="D55" t="s">
+        <v>4</v>
+      </c>
+      <c r="E55" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>83</v>
+      </c>
+      <c r="B56" t="s">
+        <v>78</v>
+      </c>
+      <c r="C56">
+        <v>2235</v>
+      </c>
+      <c r="D56" t="s">
+        <v>4</v>
+      </c>
+      <c r="E56" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>84</v>
+      </c>
+      <c r="B57" t="s">
+        <v>78</v>
+      </c>
+      <c r="C57">
+        <v>2235</v>
+      </c>
+      <c r="D57" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>85</v>
+      </c>
+      <c r="B58" t="s">
+        <v>78</v>
+      </c>
+      <c r="C58">
+        <v>2235</v>
+      </c>
+      <c r="D58" t="s">
+        <v>4</v>
+      </c>
+      <c r="E58" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>86</v>
+      </c>
+      <c r="B59" t="s">
+        <v>78</v>
+      </c>
+      <c r="C59">
+        <v>2235</v>
+      </c>
+      <c r="D59" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>87</v>
+      </c>
+      <c r="B60" t="s">
+        <v>78</v>
+      </c>
+      <c r="C60">
+        <v>2235</v>
+      </c>
+      <c r="D60" t="s">
+        <v>4</v>
+      </c>
+      <c r="E60" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>88</v>
+      </c>
+      <c r="B61" t="s">
+        <v>89</v>
+      </c>
+      <c r="C61">
+        <v>2121</v>
+      </c>
+      <c r="D61" t="s">
+        <v>4</v>
+      </c>
+      <c r="E61" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>90</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C62">
+        <v>1620</v>
+      </c>
+      <c r="D62" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>92</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63">
+        <v>34477</v>
+      </c>
+      <c r="D63" t="s">
+        <v>4</v>
+      </c>
+      <c r="E63" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>93</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C64">
+        <v>11066</v>
+      </c>
+      <c r="D64" t="s">
+        <v>4</v>
+      </c>
+      <c r="E64" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>95</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C65">
+        <v>151640</v>
+      </c>
+      <c r="D65" t="s">
+        <v>4</v>
+      </c>
+      <c r="E65" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>97</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C66">
+        <v>4572</v>
+      </c>
+      <c r="D66" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>99</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C67">
+        <v>4949</v>
+      </c>
+      <c r="D67" t="s">
+        <v>4</v>
+      </c>
+      <c r="E67" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>101</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C68">
+        <v>2567</v>
+      </c>
+      <c r="D68" t="s">
+        <v>4</v>
+      </c>
+      <c r="E68" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>103</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C69">
+        <v>2621</v>
+      </c>
+      <c r="D69" t="s">
+        <v>4</v>
+      </c>
+      <c r="E69" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>105</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C70">
+        <v>2621</v>
+      </c>
+      <c r="D70" t="s">
+        <v>4</v>
+      </c>
+      <c r="E70" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>106</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C71">
+        <v>2621</v>
+      </c>
+      <c r="D71" t="s">
+        <v>4</v>
+      </c>
+      <c r="E71" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>107</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C72">
+        <v>2621</v>
+      </c>
+      <c r="D72" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>108</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C73">
+        <v>1825</v>
+      </c>
+      <c r="D73" t="s">
+        <v>4</v>
+      </c>
+      <c r="E73" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>110</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C74">
+        <v>1825</v>
+      </c>
+      <c r="D74" t="s">
+        <v>4</v>
+      </c>
+      <c r="E74" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>111</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C75">
+        <v>4322</v>
+      </c>
+      <c r="D75" t="s">
+        <v>4</v>
+      </c>
+      <c r="E75" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>114</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C76">
+        <v>400</v>
+      </c>
+      <c r="D76" t="s">
+        <v>4</v>
+      </c>
+      <c r="E76" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>115</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C77">
+        <v>2531</v>
+      </c>
+      <c r="D77" t="s">
+        <v>4</v>
+      </c>
+      <c r="E77" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>116</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C78">
+        <v>9270</v>
+      </c>
+      <c r="D78" t="s">
+        <v>4</v>
+      </c>
+      <c r="E78" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>117</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C79">
+        <v>3271</v>
+      </c>
+      <c r="D79" t="s">
+        <v>4</v>
+      </c>
+      <c r="E79" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>119</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C80">
+        <v>16350</v>
+      </c>
+      <c r="D80" t="s">
+        <v>4</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>121</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C81">
+        <v>10291</v>
+      </c>
+      <c r="D81" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="2">
+        <v>46154</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Stok Kontrol/Eklenen.xlsx
+++ b/Stok Kontrol/Eklenen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Stok Kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77907D2-9230-4ACB-9302-059CC526DAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4060C35E-577D-489D-8388-321EAD485B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="58">
   <si>
     <t>BARKOD NUMARASI</t>
   </si>
@@ -56,190 +56,160 @@
     <t>TARİH</t>
   </si>
   <si>
-    <t>89615100-200</t>
-  </si>
-  <si>
-    <t>000000000040002349</t>
-  </si>
-  <si>
     <t>Sayılmadı</t>
   </si>
   <si>
-    <t>Sütun1</t>
-  </si>
-  <si>
-    <t>89731100-3</t>
-  </si>
-  <si>
-    <t>000000000040001376</t>
-  </si>
-  <si>
-    <t>89731100-4</t>
-  </si>
-  <si>
-    <t>89731100-5</t>
-  </si>
-  <si>
-    <t>89731300-2</t>
-  </si>
-  <si>
-    <t>000000000040001399</t>
-  </si>
-  <si>
-    <t>89756600-1</t>
-  </si>
-  <si>
-    <t>000000000040000722</t>
-  </si>
-  <si>
-    <t>89756600-2</t>
-  </si>
-  <si>
-    <t>89756600-4</t>
-  </si>
-  <si>
-    <t>89756600-5</t>
-  </si>
-  <si>
-    <t>89756600-6</t>
-  </si>
-  <si>
-    <t>89756600-7</t>
-  </si>
-  <si>
-    <t>89723900-15</t>
-  </si>
-  <si>
-    <t>000000000040001846</t>
-  </si>
-  <si>
-    <t>89756600-8</t>
-  </si>
-  <si>
-    <t>89756600-9</t>
-  </si>
-  <si>
-    <t>89743300-1</t>
-  </si>
-  <si>
-    <t>000000000040001343</t>
-  </si>
-  <si>
-    <t>89743300-2</t>
-  </si>
-  <si>
-    <t>89743300-3</t>
-  </si>
-  <si>
-    <t>89756600-3</t>
-  </si>
-  <si>
-    <t>89724100-2</t>
-  </si>
-  <si>
-    <t>000000000040001834</t>
-  </si>
-  <si>
-    <t>89722200-4</t>
-  </si>
-  <si>
-    <t>000000000040002050</t>
-  </si>
-  <si>
-    <t>89743300-7</t>
-  </si>
-  <si>
-    <t>89743300-9</t>
-  </si>
-  <si>
-    <t>89743300-11</t>
-  </si>
-  <si>
-    <t>89722500-2</t>
-  </si>
-  <si>
-    <t>000000000040001836</t>
-  </si>
-  <si>
-    <t>89743300-13</t>
-  </si>
-  <si>
-    <t>89756700-12</t>
-  </si>
-  <si>
-    <t>000000000040000754</t>
-  </si>
-  <si>
-    <t>89756700-14</t>
-  </si>
-  <si>
-    <t>89756700-16</t>
-  </si>
-  <si>
-    <t>89756700-18</t>
-  </si>
-  <si>
-    <t>89756700-19</t>
-  </si>
-  <si>
-    <t>89756700-20</t>
-  </si>
-  <si>
-    <t>89756700-21</t>
-  </si>
-  <si>
-    <t>89756700-22</t>
-  </si>
-  <si>
-    <t>89756700-25</t>
-  </si>
-  <si>
-    <t>89737100-28</t>
-  </si>
-  <si>
-    <t>000000000040000843</t>
-  </si>
-  <si>
-    <t>89763000-2</t>
-  </si>
-  <si>
-    <t>000000000040001956</t>
-  </si>
-  <si>
-    <t>89743500-15</t>
-  </si>
-  <si>
-    <t>000000000040001349</t>
-  </si>
-  <si>
-    <t>89743500-22</t>
-  </si>
-  <si>
-    <t>89756700-17</t>
-  </si>
-  <si>
-    <t>89792300-1</t>
-  </si>
-  <si>
-    <t>000000000040001364</t>
-  </si>
-  <si>
-    <t>89792300-2</t>
-  </si>
-  <si>
-    <t>89792300-3</t>
-  </si>
-  <si>
-    <t>89792300-4</t>
-  </si>
-  <si>
-    <t>89792300-5</t>
-  </si>
-  <si>
-    <t>89792300-6</t>
-  </si>
-  <si>
-    <t>89792300-7</t>
+    <t>AÇIKLAMA</t>
+  </si>
+  <si>
+    <t>89987900-44</t>
+  </si>
+  <si>
+    <t>000000000040000819</t>
+  </si>
+  <si>
+    <t>90025700-6</t>
+  </si>
+  <si>
+    <t>000000000040000626</t>
+  </si>
+  <si>
+    <t>90018100-1</t>
+  </si>
+  <si>
+    <t>000000000040001126</t>
+  </si>
+  <si>
+    <t>90044800-1</t>
+  </si>
+  <si>
+    <t>000000000040003516</t>
+  </si>
+  <si>
+    <t>90013400-1</t>
+  </si>
+  <si>
+    <t>000000000040000728</t>
+  </si>
+  <si>
+    <t>90013400-2</t>
+  </si>
+  <si>
+    <t>90013400-3</t>
+  </si>
+  <si>
+    <t>90013400-4</t>
+  </si>
+  <si>
+    <t>90013400-5</t>
+  </si>
+  <si>
+    <t>90044800-7</t>
+  </si>
+  <si>
+    <t>90044600-1</t>
+  </si>
+  <si>
+    <t>000000000040003505</t>
+  </si>
+  <si>
+    <t>90044500-1</t>
+  </si>
+  <si>
+    <t>000000000040003362</t>
+  </si>
+  <si>
+    <t>90044600-2</t>
+  </si>
+  <si>
+    <t>90044500-2</t>
+  </si>
+  <si>
+    <t>90044600-3</t>
+  </si>
+  <si>
+    <t>90044500-3</t>
+  </si>
+  <si>
+    <t>90044500-4</t>
+  </si>
+  <si>
+    <t>90044500-5</t>
+  </si>
+  <si>
+    <t>90044600-4</t>
+  </si>
+  <si>
+    <t>90044600-5</t>
+  </si>
+  <si>
+    <t>90044800-12</t>
+  </si>
+  <si>
+    <t>90044400-1</t>
+  </si>
+  <si>
+    <t>000000000040000821</t>
+  </si>
+  <si>
+    <t>90044700-1</t>
+  </si>
+  <si>
+    <t>000000000040003502</t>
+  </si>
+  <si>
+    <t>90013400-8</t>
+  </si>
+  <si>
+    <t>90013400-9</t>
+  </si>
+  <si>
+    <t>90013400-10</t>
+  </si>
+  <si>
+    <t>90044800-14</t>
+  </si>
+  <si>
+    <t>90013400-11</t>
+  </si>
+  <si>
+    <t>90013400-13</t>
+  </si>
+  <si>
+    <t>90044700-2</t>
+  </si>
+  <si>
+    <t>90044800-15</t>
+  </si>
+  <si>
+    <t>90044700-3</t>
+  </si>
+  <si>
+    <t>90044800-16</t>
+  </si>
+  <si>
+    <t>90044700-4</t>
+  </si>
+  <si>
+    <t>90044700-5</t>
+  </si>
+  <si>
+    <t>90044800-17</t>
+  </si>
+  <si>
+    <t>90044800-18</t>
+  </si>
+  <si>
+    <t>90044800-20</t>
+  </si>
+  <si>
+    <t>90044800-19</t>
+  </si>
+  <si>
+    <t>90024000-6</t>
+  </si>
+  <si>
+    <t>000000000040001802</t>
   </si>
 </sst>
 </file>
@@ -299,15 +269,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}" name="EKLENEN" displayName="EKLENEN" ref="A1:F47" totalsRowShown="0">
-  <autoFilter ref="A1:F47" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}" name="EKLENEN" displayName="EKLENEN" ref="A1:F41" totalsRowShown="0">
+  <autoFilter ref="A1:F41" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{C7FC6704-65BD-4F1E-AB57-95E929157E58}" name="BARKOD NUMARASI"/>
     <tableColumn id="2" xr3:uid="{BD785338-7565-42D3-ADE5-4B20FE7C87B3}" name="ÜRÜN KODU / ÜRÜN TANIMI"/>
     <tableColumn id="3" xr3:uid="{2ADCFFEA-69CA-4F72-B7F5-77C545583ABA}" name="MİKTAR"/>
     <tableColumn id="4" xr3:uid="{45248942-0037-4988-BF9E-9A6381298D1B}" name="BİRİM"/>
     <tableColumn id="5" xr3:uid="{58A40DAF-B543-4175-91A9-CB7572F7EF53}" name="TARİH"/>
-    <tableColumn id="6" xr3:uid="{F688B7B6-8A6C-4C03-B0E6-62ECAA2BCE68}" name="Sütun1"/>
+    <tableColumn id="6" xr3:uid="{F688B7B6-8A6C-4C03-B0E6-62ECAA2BCE68}" name="AÇIKLAMA"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -576,13 +546,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="28.5703125" customWidth="1"/>
     <col min="3" max="3" width="10.140625" customWidth="1"/>
     <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="44.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -602,387 +573,387 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2">
-        <v>28326.38</v>
+        <v>18216</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="2">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C3">
-        <v>5227</v>
+        <v>6813</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C4">
-        <v>5227</v>
+        <v>9323</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>5227</v>
+        <v>6862</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6">
-        <v>5334</v>
+        <v>3898</v>
       </c>
       <c r="D6" t="s">
         <v>4</v>
       </c>
       <c r="E6" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
       </c>
       <c r="C7">
-        <v>13394</v>
+        <v>3898</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
       </c>
       <c r="E7" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
       </c>
       <c r="C8">
-        <v>13394</v>
+        <v>3898</v>
       </c>
       <c r="D8" t="s">
         <v>4</v>
       </c>
       <c r="E8" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
       </c>
       <c r="C9">
-        <v>13394</v>
+        <v>3898</v>
       </c>
       <c r="D9" t="s">
         <v>4</v>
       </c>
       <c r="E9" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10">
-        <v>13394</v>
+        <v>3898</v>
       </c>
       <c r="D10" t="s">
         <v>4</v>
       </c>
       <c r="E10" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>13394</v>
+        <v>6862</v>
       </c>
       <c r="D11" t="s">
         <v>4</v>
       </c>
       <c r="E11" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C12">
-        <v>13394</v>
+        <v>6726</v>
       </c>
       <c r="D12" t="s">
         <v>4</v>
       </c>
       <c r="E12" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C13">
-        <v>4822</v>
+        <v>6680</v>
       </c>
       <c r="D13" t="s">
         <v>4</v>
       </c>
       <c r="E13" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F13" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C14">
-        <v>13394</v>
+        <v>6726</v>
       </c>
       <c r="D14" t="s">
         <v>4</v>
       </c>
       <c r="E14" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
         <v>26</v>
       </c>
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
       <c r="C15">
-        <v>13394</v>
+        <v>6680</v>
       </c>
       <c r="D15" t="s">
         <v>4</v>
       </c>
       <c r="E15" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C16">
-        <v>5082</v>
+        <v>6726</v>
       </c>
       <c r="D16" t="s">
         <v>4</v>
       </c>
       <c r="E16" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C17">
-        <v>5082</v>
+        <v>6680</v>
       </c>
       <c r="D17" t="s">
         <v>4</v>
       </c>
       <c r="E17" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F17" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C18">
-        <v>5082</v>
+        <v>6680</v>
       </c>
       <c r="D18" t="s">
         <v>4</v>
       </c>
       <c r="E18" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F18" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C19">
-        <v>13394</v>
+        <v>6680</v>
       </c>
       <c r="D19" t="s">
         <v>4</v>
       </c>
       <c r="E19" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C20">
-        <v>9689</v>
+        <v>6726</v>
       </c>
       <c r="D20" t="s">
         <v>4</v>
       </c>
       <c r="E20" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F20" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -990,59 +961,59 @@
         <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C21">
-        <v>18415</v>
+        <v>6726</v>
       </c>
       <c r="D21" t="s">
         <v>4</v>
       </c>
       <c r="E21" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F21" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C22">
-        <v>5082</v>
+        <v>6862</v>
       </c>
       <c r="D22" t="s">
         <v>4</v>
       </c>
       <c r="E22" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F22" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
         <v>37</v>
       </c>
-      <c r="B23" t="s">
-        <v>28</v>
-      </c>
       <c r="C23">
-        <v>5082</v>
+        <v>6524</v>
       </c>
       <c r="D23" t="s">
         <v>4</v>
       </c>
       <c r="E23" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F23" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1050,39 +1021,39 @@
         <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C24">
-        <v>5082</v>
+        <v>6726</v>
       </c>
       <c r="D24" t="s">
         <v>4</v>
       </c>
       <c r="E24" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F24" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C25">
-        <v>9452</v>
+        <v>3898</v>
       </c>
       <c r="D25" t="s">
         <v>4</v>
       </c>
       <c r="E25" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F25" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1090,19 +1061,19 @@
         <v>41</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C26">
-        <v>5082</v>
+        <v>3898</v>
       </c>
       <c r="D26" t="s">
         <v>4</v>
       </c>
       <c r="E26" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1110,419 +1081,299 @@
         <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C27">
-        <v>4573</v>
+        <v>3898</v>
       </c>
       <c r="D27" t="s">
         <v>4</v>
       </c>
       <c r="E27" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C28">
-        <v>4573</v>
+        <v>6862</v>
       </c>
       <c r="D28" t="s">
         <v>4</v>
       </c>
       <c r="E28" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F28" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C29">
-        <v>4573</v>
+        <v>3898</v>
       </c>
       <c r="D29" t="s">
         <v>4</v>
       </c>
       <c r="E29" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F29" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C30">
-        <v>4573</v>
+        <v>11696</v>
       </c>
       <c r="D30" t="s">
         <v>4</v>
       </c>
       <c r="E30" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F30" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C31">
-        <v>4573</v>
+        <v>6726</v>
       </c>
       <c r="D31" t="s">
         <v>4</v>
       </c>
       <c r="E31" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F31" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C32">
-        <v>4573</v>
+        <v>6862</v>
       </c>
       <c r="D32" t="s">
         <v>4</v>
       </c>
       <c r="E32" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C33">
-        <v>4573</v>
+        <v>6726</v>
       </c>
       <c r="D33" t="s">
         <v>4</v>
       </c>
       <c r="E33" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F33" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C34">
-        <v>4573</v>
+        <v>6862</v>
       </c>
       <c r="D34" t="s">
         <v>4</v>
       </c>
       <c r="E34" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F34" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C35">
-        <v>4573</v>
+        <v>6726</v>
       </c>
       <c r="D35" t="s">
         <v>4</v>
       </c>
       <c r="E35" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F35" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C36">
-        <v>6860</v>
+        <v>6726</v>
       </c>
       <c r="D36" t="s">
         <v>4</v>
       </c>
       <c r="E36" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F36" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="C37">
-        <v>6297</v>
+        <v>6862</v>
       </c>
       <c r="D37" t="s">
         <v>4</v>
       </c>
       <c r="E37" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F37" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
+      </c>
+      <c r="B38" t="s">
+        <v>15</v>
       </c>
       <c r="C38">
-        <v>10399</v>
+        <v>6862</v>
       </c>
       <c r="D38" t="s">
         <v>4</v>
       </c>
       <c r="E38" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F38" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="C39">
-        <v>10399</v>
+        <v>6862</v>
       </c>
       <c r="D39" t="s">
         <v>4</v>
       </c>
       <c r="E39" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F39" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>59</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
+      </c>
+      <c r="B40" t="s">
+        <v>15</v>
       </c>
       <c r="C40">
-        <v>4573</v>
+        <v>6862</v>
       </c>
       <c r="D40" t="s">
         <v>4</v>
       </c>
       <c r="E40" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F40" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C41">
-        <v>10226</v>
+        <v>5642</v>
       </c>
       <c r="D41" t="s">
         <v>4</v>
       </c>
       <c r="E41" s="2">
-        <v>46175</v>
+        <v>46204</v>
       </c>
       <c r="F41" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>62</v>
-      </c>
-      <c r="B42" t="s">
-        <v>61</v>
-      </c>
-      <c r="C42">
-        <v>10226</v>
-      </c>
-      <c r="D42" t="s">
-        <v>4</v>
-      </c>
-      <c r="E42" s="2">
-        <v>46175</v>
-      </c>
-      <c r="F42" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>63</v>
-      </c>
-      <c r="B43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43">
-        <v>10226</v>
-      </c>
-      <c r="D43" t="s">
-        <v>4</v>
-      </c>
-      <c r="E43" s="2">
-        <v>46175</v>
-      </c>
-      <c r="F43" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>64</v>
-      </c>
-      <c r="B44" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44">
-        <v>10226</v>
-      </c>
-      <c r="D44" t="s">
-        <v>4</v>
-      </c>
-      <c r="E44" s="2">
-        <v>46175</v>
-      </c>
-      <c r="F44" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>65</v>
-      </c>
-      <c r="B45" t="s">
-        <v>61</v>
-      </c>
-      <c r="C45">
-        <v>10226</v>
-      </c>
-      <c r="D45" t="s">
-        <v>4</v>
-      </c>
-      <c r="E45" s="2">
-        <v>46175</v>
-      </c>
-      <c r="F45" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>66</v>
-      </c>
-      <c r="B46" t="s">
-        <v>61</v>
-      </c>
-      <c r="C46">
-        <v>10226</v>
-      </c>
-      <c r="D46" t="s">
-        <v>4</v>
-      </c>
-      <c r="E46" s="2">
-        <v>46175</v>
-      </c>
-      <c r="F46" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>67</v>
-      </c>
-      <c r="B47" t="s">
-        <v>61</v>
-      </c>
-      <c r="C47">
-        <v>10226</v>
-      </c>
-      <c r="D47" t="s">
-        <v>4</v>
-      </c>
-      <c r="E47" s="2">
-        <v>46175</v>
-      </c>
-      <c r="F47" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Stok Kontrol/Eklenen.xlsx
+++ b/Stok Kontrol/Eklenen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Stok Kontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4060C35E-577D-489D-8388-321EAD485B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52ABCBD3-E99A-4606-9BBC-2716666C0B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="75">
   <si>
     <t>BARKOD NUMARASI</t>
   </si>
@@ -62,154 +62,205 @@
     <t>AÇIKLAMA</t>
   </si>
   <si>
-    <t>89987900-44</t>
-  </si>
-  <si>
-    <t>000000000040000819</t>
-  </si>
-  <si>
-    <t>90025700-6</t>
-  </si>
-  <si>
-    <t>000000000040000626</t>
-  </si>
-  <si>
-    <t>90018100-1</t>
-  </si>
-  <si>
-    <t>000000000040001126</t>
-  </si>
-  <si>
-    <t>90044800-1</t>
-  </si>
-  <si>
-    <t>000000000040003516</t>
-  </si>
-  <si>
-    <t>90013400-1</t>
-  </si>
-  <si>
-    <t>000000000040000728</t>
-  </si>
-  <si>
-    <t>90013400-2</t>
-  </si>
-  <si>
-    <t>90013400-3</t>
-  </si>
-  <si>
-    <t>90013400-4</t>
-  </si>
-  <si>
-    <t>90013400-5</t>
-  </si>
-  <si>
-    <t>90044800-7</t>
-  </si>
-  <si>
-    <t>90044600-1</t>
-  </si>
-  <si>
-    <t>000000000040003505</t>
-  </si>
-  <si>
-    <t>90044500-1</t>
+    <t>90257300-4</t>
+  </si>
+  <si>
+    <t>000000000040002657</t>
+  </si>
+  <si>
+    <t>90257400-47</t>
+  </si>
+  <si>
+    <t>000000000040002656</t>
+  </si>
+  <si>
+    <t>90257400-44</t>
+  </si>
+  <si>
+    <t>90257400-54</t>
+  </si>
+  <si>
+    <t>90257400-52</t>
+  </si>
+  <si>
+    <t>90257400-9</t>
+  </si>
+  <si>
+    <t>90257400-48</t>
+  </si>
+  <si>
+    <t>90300700-3</t>
+  </si>
+  <si>
+    <t>000000000040002699</t>
+  </si>
+  <si>
+    <t>DFS</t>
+  </si>
+  <si>
+    <t>90179002-12</t>
+  </si>
+  <si>
+    <t>000000000045007347</t>
+  </si>
+  <si>
+    <t>90275100-5</t>
+  </si>
+  <si>
+    <t>000000000040001398</t>
+  </si>
+  <si>
+    <t>90298000-3</t>
+  </si>
+  <si>
+    <t>000000000045055294</t>
+  </si>
+  <si>
+    <t>90297900-1</t>
+  </si>
+  <si>
+    <t>000000000045055293</t>
+  </si>
+  <si>
+    <t>90264500-1</t>
+  </si>
+  <si>
+    <t>000000000045045212</t>
+  </si>
+  <si>
+    <t>90300700-1</t>
+  </si>
+  <si>
+    <t>90280800-4</t>
+  </si>
+  <si>
+    <t>000000000040001371</t>
+  </si>
+  <si>
+    <t>90296300-4</t>
+  </si>
+  <si>
+    <t>000000000045052672</t>
+  </si>
+  <si>
+    <t>90296300-5</t>
+  </si>
+  <si>
+    <t>90296300-6</t>
+  </si>
+  <si>
+    <t>Teyitsiz gözüküyor.</t>
+  </si>
+  <si>
+    <t>90296300-1</t>
+  </si>
+  <si>
+    <t>90296300-3</t>
+  </si>
+  <si>
+    <t>90296300-2</t>
+  </si>
+  <si>
+    <t>90296200-1</t>
+  </si>
+  <si>
+    <t>000000000045055775</t>
+  </si>
+  <si>
+    <t>Ters kayıt</t>
+  </si>
+  <si>
+    <t>90273600-2</t>
+  </si>
+  <si>
+    <t>000000000040001362</t>
+  </si>
+  <si>
+    <t>90290500-1</t>
+  </si>
+  <si>
+    <t>000000000045054682</t>
+  </si>
+  <si>
+    <t>90221800-1</t>
+  </si>
+  <si>
+    <t>90221800-2</t>
+  </si>
+  <si>
+    <t>90221800-3</t>
+  </si>
+  <si>
+    <t>90221800-4</t>
+  </si>
+  <si>
+    <t>90221800-5</t>
+  </si>
+  <si>
+    <t>000000000040002934</t>
+  </si>
+  <si>
+    <t>90251000-11</t>
+  </si>
+  <si>
+    <t>000000000040001110</t>
+  </si>
+  <si>
+    <t>90251100-24</t>
+  </si>
+  <si>
+    <t>90251100-25</t>
+  </si>
+  <si>
+    <t>Halat isteği üzerine</t>
+  </si>
+  <si>
+    <t>90383800-1</t>
+  </si>
+  <si>
+    <t>000000000040002584</t>
+  </si>
+  <si>
+    <t>90383800-2</t>
+  </si>
+  <si>
+    <t>90293500-19</t>
+  </si>
+  <si>
+    <t>000000000040000724</t>
+  </si>
+  <si>
+    <t>90114800-11</t>
+  </si>
+  <si>
+    <t>000000000040002679</t>
+  </si>
+  <si>
+    <t>90277000-22</t>
   </si>
   <si>
     <t>000000000040003362</t>
   </si>
   <si>
-    <t>90044600-2</t>
-  </si>
-  <si>
-    <t>90044500-2</t>
-  </si>
-  <si>
-    <t>90044600-3</t>
-  </si>
-  <si>
-    <t>90044500-3</t>
-  </si>
-  <si>
-    <t>90044500-4</t>
-  </si>
-  <si>
-    <t>90044500-5</t>
-  </si>
-  <si>
-    <t>90044600-4</t>
-  </si>
-  <si>
-    <t>90044600-5</t>
-  </si>
-  <si>
-    <t>90044800-12</t>
-  </si>
-  <si>
-    <t>90044400-1</t>
-  </si>
-  <si>
-    <t>000000000040000821</t>
-  </si>
-  <si>
-    <t>90044700-1</t>
-  </si>
-  <si>
-    <t>000000000040003502</t>
-  </si>
-  <si>
-    <t>90013400-8</t>
-  </si>
-  <si>
-    <t>90013400-9</t>
-  </si>
-  <si>
-    <t>90013400-10</t>
-  </si>
-  <si>
-    <t>90044800-14</t>
-  </si>
-  <si>
-    <t>90013400-11</t>
-  </si>
-  <si>
-    <t>90013400-13</t>
-  </si>
-  <si>
-    <t>90044700-2</t>
-  </si>
-  <si>
-    <t>90044800-15</t>
-  </si>
-  <si>
-    <t>90044700-3</t>
-  </si>
-  <si>
-    <t>90044800-16</t>
-  </si>
-  <si>
-    <t>90044700-4</t>
-  </si>
-  <si>
-    <t>90044700-5</t>
-  </si>
-  <si>
-    <t>90044800-17</t>
-  </si>
-  <si>
-    <t>90044800-18</t>
-  </si>
-  <si>
-    <t>90044800-20</t>
-  </si>
-  <si>
-    <t>90044800-19</t>
-  </si>
-  <si>
-    <t>90024000-6</t>
-  </si>
-  <si>
-    <t>000000000040001802</t>
+    <t>90308400-5</t>
+  </si>
+  <si>
+    <t>000000000045055381</t>
+  </si>
+  <si>
+    <t>90288400-1</t>
+  </si>
+  <si>
+    <t>000000000040002698</t>
+  </si>
+  <si>
+    <t>90288400-2</t>
+  </si>
+  <si>
+    <t>90288400-3</t>
+  </si>
+  <si>
+    <t>90288400-4</t>
   </si>
 </sst>
 </file>
@@ -245,10 +296,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -269,8 +321,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}" name="EKLENEN" displayName="EKLENEN" ref="A1:F41" totalsRowShown="0">
-  <autoFilter ref="A1:F41" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}" name="EKLENEN" displayName="EKLENEN" ref="A1:F46" totalsRowShown="0">
+  <autoFilter ref="A1:F46" xr:uid="{25C5C167-F782-4D50-9FF8-811AA4D4B559}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{C7FC6704-65BD-4F1E-AB57-95E929157E58}" name="BARKOD NUMARASI"/>
     <tableColumn id="2" xr3:uid="{BD785338-7565-42D3-ADE5-4B20FE7C87B3}" name="ÜRÜN KODU / ÜRÜN TANIMI"/>
@@ -546,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -583,14 +635,14 @@
       <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2">
-        <v>18216</v>
+      <c r="C2" s="3">
+        <v>21017</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="2">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="F2" t="s">
         <v>6</v>
@@ -600,17 +652,17 @@
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>11</v>
       </c>
       <c r="C3">
-        <v>6813</v>
+        <v>21257</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="2">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="F3" t="s">
         <v>6</v>
@@ -620,17 +672,17 @@
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
+      <c r="B4" t="s">
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>9323</v>
+        <v>21257</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="2">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="F4" t="s">
         <v>6</v>
@@ -638,19 +690,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>6862</v>
+        <v>21257</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="2">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="F5" t="s">
         <v>6</v>
@@ -658,19 +710,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>3898</v>
+        <v>21257</v>
       </c>
       <c r="D6" t="s">
         <v>4</v>
       </c>
       <c r="E6" s="2">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="F6" t="s">
         <v>6</v>
@@ -678,19 +730,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>3898</v>
+        <v>21257</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
       </c>
       <c r="E7" s="2">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="F7" t="s">
         <v>6</v>
@@ -698,19 +750,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>3898</v>
+        <v>21257</v>
       </c>
       <c r="D8" t="s">
         <v>4</v>
       </c>
       <c r="E8" s="2">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="F8" t="s">
         <v>6</v>
@@ -718,39 +770,39 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C9">
-        <v>3898</v>
+      <c r="B9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3">
+        <v>18755</v>
       </c>
       <c r="D9" t="s">
         <v>4</v>
       </c>
       <c r="E9" s="2">
-        <v>46204</v>
+        <v>46237</v>
       </c>
       <c r="F9" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
       <c r="C10">
-        <v>3898</v>
+        <v>5420</v>
       </c>
       <c r="D10" t="s">
         <v>4</v>
       </c>
       <c r="E10" s="2">
-        <v>46204</v>
+        <v>46237</v>
       </c>
       <c r="F10" t="s">
         <v>6</v>
@@ -760,17 +812,17 @@
       <c r="A11" t="s">
         <v>22</v>
       </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11">
-        <v>6862</v>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="3">
+        <v>5022</v>
       </c>
       <c r="D11" t="s">
         <v>4</v>
       </c>
       <c r="E11" s="2">
-        <v>46204</v>
+        <v>46237</v>
       </c>
       <c r="F11" t="s">
         <v>6</v>
@@ -778,19 +830,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
         <v>24</v>
       </c>
-      <c r="C12">
-        <v>6726</v>
+      <c r="B12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1328</v>
       </c>
       <c r="D12" t="s">
         <v>4</v>
       </c>
       <c r="E12" s="2">
-        <v>46204</v>
+        <v>46237</v>
       </c>
       <c r="F12" t="s">
         <v>6</v>
@@ -798,19 +850,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13">
-        <v>6680</v>
+        <v>1260</v>
       </c>
       <c r="D13" t="s">
         <v>4</v>
       </c>
       <c r="E13" s="2">
-        <v>46204</v>
+        <v>46237</v>
       </c>
       <c r="F13" t="s">
         <v>6</v>
@@ -818,19 +870,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C14">
-        <v>6726</v>
+        <v>1655</v>
       </c>
       <c r="D14" t="s">
         <v>4</v>
       </c>
       <c r="E14" s="2">
-        <v>46204</v>
+        <v>46237</v>
       </c>
       <c r="F14" t="s">
         <v>6</v>
@@ -838,19 +890,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
+        <v>30</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="C15">
-        <v>6680</v>
+        <v>2406</v>
       </c>
       <c r="D15" t="s">
         <v>4</v>
       </c>
       <c r="E15" s="2">
-        <v>46204</v>
+        <v>46237</v>
       </c>
       <c r="F15" t="s">
         <v>6</v>
@@ -858,19 +910,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16">
-        <v>6726</v>
+        <v>31</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="3">
+        <v>4900</v>
       </c>
       <c r="D16" t="s">
         <v>4</v>
       </c>
       <c r="E16" s="2">
-        <v>46204</v>
+        <v>46238</v>
       </c>
       <c r="F16" t="s">
         <v>6</v>
@@ -878,162 +930,162 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17">
-        <v>6680</v>
+        <v>33</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3236</v>
       </c>
       <c r="D17" t="s">
         <v>4</v>
       </c>
       <c r="E17" s="2">
-        <v>46204</v>
+        <v>46238</v>
       </c>
       <c r="F17" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C18">
-        <v>6680</v>
+        <v>3236</v>
       </c>
       <c r="D18" t="s">
         <v>4</v>
       </c>
       <c r="E18" s="2">
-        <v>46204</v>
+        <v>46238</v>
       </c>
       <c r="F18" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C19">
-        <v>6680</v>
+        <v>3236</v>
       </c>
       <c r="D19" t="s">
         <v>4</v>
       </c>
       <c r="E19" s="2">
-        <v>46204</v>
+        <v>46238</v>
       </c>
       <c r="F19" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20">
-        <v>6726</v>
+        <v>35</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="3">
+        <v>3236</v>
       </c>
       <c r="D20" t="s">
         <v>4</v>
       </c>
       <c r="E20" s="2">
-        <v>46204</v>
+        <v>46238</v>
       </c>
       <c r="F20" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
         <v>34</v>
       </c>
-      <c r="B21" t="s">
-        <v>24</v>
-      </c>
       <c r="C21">
-        <v>6726</v>
+        <v>3236</v>
       </c>
       <c r="D21" t="s">
         <v>4</v>
       </c>
       <c r="E21" s="2">
-        <v>46204</v>
+        <v>46238</v>
       </c>
       <c r="F21" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C22">
-        <v>6862</v>
+        <v>3236</v>
       </c>
       <c r="D22" t="s">
         <v>4</v>
       </c>
       <c r="E22" s="2">
-        <v>46204</v>
+        <v>46238</v>
       </c>
       <c r="F22" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C23">
-        <v>6524</v>
+        <v>3236</v>
       </c>
       <c r="D23" t="s">
         <v>4</v>
       </c>
       <c r="E23" s="2">
-        <v>46204</v>
+        <v>46238</v>
       </c>
       <c r="F23" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C24">
-        <v>6726</v>
+        <v>3236</v>
       </c>
       <c r="D24" t="s">
         <v>4</v>
       </c>
       <c r="E24" s="2">
-        <v>46204</v>
+        <v>46238</v>
       </c>
       <c r="F24" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1041,19 +1093,19 @@
         <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C25">
-        <v>3898</v>
+        <v>3236</v>
       </c>
       <c r="D25" t="s">
         <v>4</v>
       </c>
       <c r="E25" s="2">
-        <v>46204</v>
+        <v>46238</v>
       </c>
       <c r="F25" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1061,36 +1113,36 @@
         <v>41</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="C26">
-        <v>3898</v>
+        <v>3046</v>
       </c>
       <c r="D26" t="s">
         <v>4</v>
       </c>
       <c r="E26" s="2">
-        <v>46204</v>
+        <v>46238</v>
       </c>
       <c r="F26" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C27">
-        <v>3898</v>
+        <v>6939</v>
       </c>
       <c r="D27" t="s">
         <v>4</v>
       </c>
       <c r="E27" s="2">
-        <v>46204</v>
+        <v>46239</v>
       </c>
       <c r="F27" t="s">
         <v>6</v>
@@ -1098,19 +1150,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="C28">
-        <v>6862</v>
+        <v>3236</v>
       </c>
       <c r="D28" t="s">
         <v>4</v>
       </c>
       <c r="E28" s="2">
-        <v>46204</v>
+        <v>46239</v>
       </c>
       <c r="F28" t="s">
         <v>6</v>
@@ -1118,119 +1170,119 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="C29">
-        <v>3898</v>
+        <v>3500</v>
       </c>
       <c r="D29" t="s">
         <v>4</v>
       </c>
       <c r="E29" s="2">
-        <v>46204</v>
+        <v>46239</v>
       </c>
       <c r="F29" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="C30">
-        <v>11696</v>
+        <v>4000</v>
       </c>
       <c r="D30" t="s">
         <v>4</v>
       </c>
       <c r="E30" s="2">
-        <v>46204</v>
+        <v>46239</v>
       </c>
       <c r="F30" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C31">
-        <v>6726</v>
+        <v>3200</v>
       </c>
       <c r="D31" t="s">
         <v>4</v>
       </c>
       <c r="E31" s="2">
-        <v>46204</v>
+        <v>46239</v>
       </c>
       <c r="F31" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="C32">
-        <v>6862</v>
+        <v>3600</v>
       </c>
       <c r="D32" t="s">
         <v>4</v>
       </c>
       <c r="E32" s="2">
-        <v>46204</v>
+        <v>46239</v>
       </c>
       <c r="F32" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C33">
-        <v>6726</v>
+        <v>3600</v>
       </c>
       <c r="D33" t="s">
         <v>4</v>
       </c>
       <c r="E33" s="2">
-        <v>46204</v>
+        <v>46239</v>
       </c>
       <c r="F33" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="C34">
-        <v>6862</v>
+        <v>4072</v>
       </c>
       <c r="D34" t="s">
         <v>4</v>
       </c>
       <c r="E34" s="2">
-        <v>46204</v>
+        <v>46239</v>
       </c>
       <c r="F34" t="s">
         <v>6</v>
@@ -1238,19 +1290,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
-      </c>
-      <c r="B35" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35">
-        <v>6726</v>
+        <v>56</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="3">
+        <v>4129</v>
       </c>
       <c r="D35" t="s">
         <v>4</v>
       </c>
       <c r="E35" s="2">
-        <v>46204</v>
+        <v>46239</v>
       </c>
       <c r="F35" t="s">
         <v>6</v>
@@ -1258,79 +1310,79 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36">
-        <v>6726</v>
+        <v>57</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="3">
+        <v>4129</v>
       </c>
       <c r="D36" t="s">
         <v>4</v>
       </c>
       <c r="E36" s="2">
-        <v>46204</v>
+        <v>46239</v>
       </c>
       <c r="F36" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>52</v>
-      </c>
-      <c r="B37" t="s">
-        <v>15</v>
-      </c>
-      <c r="C37">
-        <v>6862</v>
+        <v>59</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" s="3">
+        <v>21552</v>
       </c>
       <c r="D37" t="s">
         <v>4</v>
       </c>
       <c r="E37" s="2">
-        <v>46204</v>
+        <v>46239</v>
       </c>
       <c r="F37" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>53</v>
-      </c>
-      <c r="B38" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38">
-        <v>6862</v>
+        <v>61</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" s="3">
+        <v>21552</v>
       </c>
       <c r="D38" t="s">
         <v>4</v>
       </c>
       <c r="E38" s="2">
-        <v>46204</v>
+        <v>46239</v>
       </c>
       <c r="F38" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39" t="s">
-        <v>15</v>
-      </c>
-      <c r="C39">
-        <v>6862</v>
+        <v>62</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="3">
+        <v>13388</v>
       </c>
       <c r="D39" t="s">
         <v>4</v>
       </c>
       <c r="E39" s="2">
-        <v>46204</v>
+        <v>46241</v>
       </c>
       <c r="F39" t="s">
         <v>6</v>
@@ -1338,42 +1390,142 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="C40">
-        <v>6862</v>
+        <v>6025</v>
       </c>
       <c r="D40" t="s">
         <v>4</v>
       </c>
       <c r="E40" s="2">
-        <v>46204</v>
+        <v>46241</v>
       </c>
       <c r="F40" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C41">
-        <v>5642</v>
+        <v>17892</v>
       </c>
       <c r="D41" t="s">
         <v>4</v>
       </c>
       <c r="E41" s="2">
-        <v>46204</v>
+        <v>46242</v>
       </c>
       <c r="F41" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>68</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="3">
+        <v>2233</v>
+      </c>
+      <c r="D42" t="s">
+        <v>4</v>
+      </c>
+      <c r="E42" s="2">
+        <v>46244</v>
+      </c>
+      <c r="F42" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43">
+        <v>9200</v>
+      </c>
+      <c r="D43" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="2">
+        <v>46244</v>
+      </c>
+      <c r="F43" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>72</v>
+      </c>
+      <c r="B44" t="s">
+        <v>71</v>
+      </c>
+      <c r="C44">
+        <v>9150</v>
+      </c>
+      <c r="D44" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="2">
+        <v>46244</v>
+      </c>
+      <c r="F44" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45">
+        <v>9200</v>
+      </c>
+      <c r="D45" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="2">
+        <v>46244</v>
+      </c>
+      <c r="F45" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>74</v>
+      </c>
+      <c r="B46" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46">
+        <v>9150</v>
+      </c>
+      <c r="D46" t="s">
+        <v>4</v>
+      </c>
+      <c r="E46" s="2">
+        <v>46244</v>
+      </c>
+      <c r="F46" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
